--- a/data/DATRAS_EggsLarvae_conversion.xlsx
+++ b/data/DATRAS_EggsLarvae_conversion.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wurnet.nl\dfs-root\IMARES\IJmuiden\WOT\WOT surveys Zout - Haringlarven\Down's recruitment survey\New index calculation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\git\eggsandlarvae\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C19FFB8A-D125-401E-A106-549DE7CFEEC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F083BF15-4999-4859-81A9-C4EEBEABAEAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8016" yWindow="0" windowWidth="14568" windowHeight="12360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HH-EH" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="167">
   <si>
     <t>No</t>
   </si>
@@ -530,6 +530,12 @@
   </si>
   <si>
     <t>PreservationMethod</t>
+  </si>
+  <si>
+    <t>chat</t>
+  </si>
+  <si>
+    <t>RaisingFactor</t>
   </si>
 </sst>
 </file>
@@ -1048,41 +1054,34 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1143,215 +1142,215 @@
 </file>
 
 <file path=xl/activeX/activeX1.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStreamInit" r:id="rId1"/>
 </file>
 
 <file path=xl/activeX/activeX10.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStreamInit" r:id="rId1"/>
 </file>
 
 <file path=xl/activeX/activeX11.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStreamInit" r:id="rId1"/>
 </file>
 
 <file path=xl/activeX/activeX12.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStreamInit" r:id="rId1"/>
 </file>
 
 <file path=xl/activeX/activeX13.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStreamInit" r:id="rId1"/>
 </file>
 
 <file path=xl/activeX/activeX14.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStreamInit" r:id="rId1"/>
 </file>
 
 <file path=xl/activeX/activeX15.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStreamInit" r:id="rId1"/>
 </file>
 
 <file path=xl/activeX/activeX16.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStreamInit" r:id="rId1"/>
 </file>
 
 <file path=xl/activeX/activeX17.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStreamInit" r:id="rId1"/>
 </file>
 
 <file path=xl/activeX/activeX18.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStreamInit" r:id="rId1"/>
 </file>
 
 <file path=xl/activeX/activeX19.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStreamInit" r:id="rId1"/>
 </file>
 
 <file path=xl/activeX/activeX2.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStreamInit" r:id="rId1"/>
 </file>
 
 <file path=xl/activeX/activeX20.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStreamInit" r:id="rId1"/>
 </file>
 
 <file path=xl/activeX/activeX21.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStreamInit" r:id="rId1"/>
 </file>
 
 <file path=xl/activeX/activeX22.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStreamInit" r:id="rId1"/>
 </file>
 
 <file path=xl/activeX/activeX23.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStreamInit" r:id="rId1"/>
 </file>
 
 <file path=xl/activeX/activeX24.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStreamInit" r:id="rId1"/>
 </file>
 
 <file path=xl/activeX/activeX25.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStreamInit" r:id="rId1"/>
 </file>
 
 <file path=xl/activeX/activeX26.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStreamInit" r:id="rId1"/>
 </file>
 
 <file path=xl/activeX/activeX27.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStreamInit" r:id="rId1"/>
 </file>
 
 <file path=xl/activeX/activeX28.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStreamInit" r:id="rId1"/>
 </file>
 
 <file path=xl/activeX/activeX29.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStreamInit" r:id="rId1"/>
 </file>
 
 <file path=xl/activeX/activeX3.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStreamInit" r:id="rId1"/>
 </file>
 
 <file path=xl/activeX/activeX30.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStreamInit" r:id="rId1"/>
 </file>
 
 <file path=xl/activeX/activeX31.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStreamInit" r:id="rId1"/>
 </file>
 
 <file path=xl/activeX/activeX32.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStreamInit" r:id="rId1"/>
 </file>
 
 <file path=xl/activeX/activeX33.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStreamInit" r:id="rId1"/>
 </file>
 
 <file path=xl/activeX/activeX34.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStreamInit" r:id="rId1"/>
 </file>
 
 <file path=xl/activeX/activeX35.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStreamInit" r:id="rId1"/>
 </file>
 
 <file path=xl/activeX/activeX36.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStreamInit" r:id="rId1"/>
 </file>
 
 <file path=xl/activeX/activeX37.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStreamInit" r:id="rId1"/>
 </file>
 
 <file path=xl/activeX/activeX38.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStreamInit" r:id="rId1"/>
 </file>
 
 <file path=xl/activeX/activeX39.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStreamInit" r:id="rId1"/>
 </file>
 
 <file path=xl/activeX/activeX4.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStreamInit" r:id="rId1"/>
 </file>
 
 <file path=xl/activeX/activeX40.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStreamInit" r:id="rId1"/>
 </file>
 
 <file path=xl/activeX/activeX41.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStreamInit" r:id="rId1"/>
 </file>
 
 <file path=xl/activeX/activeX42.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStreamInit" r:id="rId1"/>
 </file>
 
 <file path=xl/activeX/activeX43.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStreamInit" r:id="rId1"/>
 </file>
 
 <file path=xl/activeX/activeX44.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStreamInit" r:id="rId1"/>
 </file>
 
 <file path=xl/activeX/activeX45.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStreamInit" r:id="rId1"/>
 </file>
 
 <file path=xl/activeX/activeX46.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStreamInit" r:id="rId1"/>
 </file>
 
 <file path=xl/activeX/activeX47.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStreamInit" r:id="rId1"/>
 </file>
 
 <file path=xl/activeX/activeX48.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStreamInit" r:id="rId1"/>
 </file>
 
 <file path=xl/activeX/activeX49.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStreamInit" r:id="rId1"/>
 </file>
 
 <file path=xl/activeX/activeX5.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStreamInit" r:id="rId1"/>
 </file>
 
 <file path=xl/activeX/activeX50.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStreamInit" r:id="rId1"/>
 </file>
 
 <file path=xl/activeX/activeX51.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStreamInit" r:id="rId1"/>
 </file>
 
 <file path=xl/activeX/activeX52.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStreamInit" r:id="rId1"/>
 </file>
 
 <file path=xl/activeX/activeX53.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStreamInit" r:id="rId1"/>
 </file>
 
 <file path=xl/activeX/activeX6.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStreamInit" r:id="rId1"/>
 </file>
 
 <file path=xl/activeX/activeX7.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStreamInit" r:id="rId1"/>
 </file>
 
 <file path=xl/activeX/activeX8.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStreamInit" r:id="rId1"/>
 </file>
 
 <file path=xl/activeX/activeX9.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStreamInit" r:id="rId1"/>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1367,9 +1366,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>16</xdr:col>
-          <xdr:colOff>228600</xdr:colOff>
+          <xdr:colOff>257175</xdr:colOff>
           <xdr:row>3</xdr:row>
-          <xdr:rowOff>53340</xdr:rowOff>
+          <xdr:rowOff>76200</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -1412,14 +1411,14 @@
         <xdr:from>
           <xdr:col>16</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>3</xdr:row>
+          <xdr:row>4</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>16</xdr:col>
-          <xdr:colOff>228600</xdr:colOff>
-          <xdr:row>4</xdr:row>
-          <xdr:rowOff>60960</xdr:rowOff>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>5</xdr:row>
+          <xdr:rowOff>76200</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -1462,14 +1461,14 @@
         <xdr:from>
           <xdr:col>16</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>4</xdr:row>
+          <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>16</xdr:col>
-          <xdr:colOff>228600</xdr:colOff>
-          <xdr:row>5</xdr:row>
-          <xdr:rowOff>60960</xdr:rowOff>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>6</xdr:row>
+          <xdr:rowOff>76200</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -1512,14 +1511,14 @@
         <xdr:from>
           <xdr:col>16</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>5</xdr:row>
+          <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>16</xdr:col>
-          <xdr:colOff>228600</xdr:colOff>
-          <xdr:row>6</xdr:row>
-          <xdr:rowOff>60960</xdr:rowOff>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>7</xdr:row>
+          <xdr:rowOff>76200</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -1562,14 +1561,14 @@
         <xdr:from>
           <xdr:col>16</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>6</xdr:row>
+          <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>16</xdr:col>
-          <xdr:colOff>228600</xdr:colOff>
-          <xdr:row>7</xdr:row>
-          <xdr:rowOff>60960</xdr:rowOff>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>8</xdr:row>
+          <xdr:rowOff>76200</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -1612,14 +1611,14 @@
         <xdr:from>
           <xdr:col>16</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>7</xdr:row>
+          <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>16</xdr:col>
-          <xdr:colOff>228600</xdr:colOff>
-          <xdr:row>8</xdr:row>
-          <xdr:rowOff>60960</xdr:rowOff>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>9</xdr:row>
+          <xdr:rowOff>76200</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -1662,14 +1661,14 @@
         <xdr:from>
           <xdr:col>16</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>8</xdr:row>
+          <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>16</xdr:col>
-          <xdr:colOff>228600</xdr:colOff>
-          <xdr:row>9</xdr:row>
-          <xdr:rowOff>60960</xdr:rowOff>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>10</xdr:row>
+          <xdr:rowOff>76200</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -1712,14 +1711,14 @@
         <xdr:from>
           <xdr:col>16</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>9</xdr:row>
+          <xdr:row>10</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>16</xdr:col>
-          <xdr:colOff>228600</xdr:colOff>
-          <xdr:row>10</xdr:row>
-          <xdr:rowOff>53340</xdr:rowOff>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>11</xdr:row>
+          <xdr:rowOff>66675</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -1762,14 +1761,14 @@
         <xdr:from>
           <xdr:col>16</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>10</xdr:row>
+          <xdr:row>11</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>16</xdr:col>
-          <xdr:colOff>228600</xdr:colOff>
-          <xdr:row>11</xdr:row>
-          <xdr:rowOff>53340</xdr:rowOff>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>12</xdr:row>
+          <xdr:rowOff>66675</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -1812,14 +1811,14 @@
         <xdr:from>
           <xdr:col>16</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>11</xdr:row>
+          <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>16</xdr:col>
-          <xdr:colOff>228600</xdr:colOff>
-          <xdr:row>12</xdr:row>
-          <xdr:rowOff>53340</xdr:rowOff>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>13</xdr:row>
+          <xdr:rowOff>66675</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -1862,14 +1861,14 @@
         <xdr:from>
           <xdr:col>16</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>12</xdr:row>
+          <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>16</xdr:col>
-          <xdr:colOff>228600</xdr:colOff>
-          <xdr:row>13</xdr:row>
-          <xdr:rowOff>53340</xdr:rowOff>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>14</xdr:row>
+          <xdr:rowOff>66675</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -1912,14 +1911,14 @@
         <xdr:from>
           <xdr:col>16</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>13</xdr:row>
+          <xdr:row>14</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>16</xdr:col>
-          <xdr:colOff>228600</xdr:colOff>
-          <xdr:row>14</xdr:row>
-          <xdr:rowOff>53340</xdr:rowOff>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>15</xdr:row>
+          <xdr:rowOff>66675</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -1962,14 +1961,14 @@
         <xdr:from>
           <xdr:col>16</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>14</xdr:row>
+          <xdr:row>15</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>16</xdr:col>
-          <xdr:colOff>228600</xdr:colOff>
-          <xdr:row>15</xdr:row>
-          <xdr:rowOff>53340</xdr:rowOff>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>16</xdr:row>
+          <xdr:rowOff>66675</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2012,14 +2011,14 @@
         <xdr:from>
           <xdr:col>16</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>15</xdr:row>
+          <xdr:row>16</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>16</xdr:col>
-          <xdr:colOff>228600</xdr:colOff>
-          <xdr:row>16</xdr:row>
-          <xdr:rowOff>53340</xdr:rowOff>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>17</xdr:row>
+          <xdr:rowOff>66675</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2062,14 +2061,14 @@
         <xdr:from>
           <xdr:col>16</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>17</xdr:row>
+          <xdr:row>18</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>16</xdr:col>
-          <xdr:colOff>228600</xdr:colOff>
-          <xdr:row>18</xdr:row>
-          <xdr:rowOff>53340</xdr:rowOff>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>19</xdr:row>
+          <xdr:rowOff>66675</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2112,14 +2111,14 @@
         <xdr:from>
           <xdr:col>16</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>18</xdr:row>
+          <xdr:row>19</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>16</xdr:col>
-          <xdr:colOff>228600</xdr:colOff>
-          <xdr:row>19</xdr:row>
-          <xdr:rowOff>53340</xdr:rowOff>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>20</xdr:row>
+          <xdr:rowOff>66675</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2162,14 +2161,14 @@
         <xdr:from>
           <xdr:col>16</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>20</xdr:row>
+          <xdr:row>21</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>16</xdr:col>
-          <xdr:colOff>228600</xdr:colOff>
-          <xdr:row>21</xdr:row>
-          <xdr:rowOff>53340</xdr:rowOff>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>22</xdr:row>
+          <xdr:rowOff>66675</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2212,14 +2211,14 @@
         <xdr:from>
           <xdr:col>16</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>21</xdr:row>
+          <xdr:row>22</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>16</xdr:col>
-          <xdr:colOff>228600</xdr:colOff>
-          <xdr:row>22</xdr:row>
-          <xdr:rowOff>53340</xdr:rowOff>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>23</xdr:row>
+          <xdr:rowOff>66675</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2262,14 +2261,14 @@
         <xdr:from>
           <xdr:col>16</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>22</xdr:row>
+          <xdr:row>23</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>16</xdr:col>
-          <xdr:colOff>228600</xdr:colOff>
-          <xdr:row>23</xdr:row>
-          <xdr:rowOff>60960</xdr:rowOff>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>24</xdr:row>
+          <xdr:rowOff>76200</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2312,14 +2311,14 @@
         <xdr:from>
           <xdr:col>16</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>23</xdr:row>
+          <xdr:row>24</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>16</xdr:col>
-          <xdr:colOff>228600</xdr:colOff>
-          <xdr:row>24</xdr:row>
-          <xdr:rowOff>60960</xdr:rowOff>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>25</xdr:row>
+          <xdr:rowOff>76200</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2362,14 +2361,14 @@
         <xdr:from>
           <xdr:col>16</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>24</xdr:row>
+          <xdr:row>25</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>16</xdr:col>
-          <xdr:colOff>228600</xdr:colOff>
-          <xdr:row>25</xdr:row>
-          <xdr:rowOff>53340</xdr:rowOff>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>26</xdr:row>
+          <xdr:rowOff>66675</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2412,14 +2411,14 @@
         <xdr:from>
           <xdr:col>16</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>25</xdr:row>
+          <xdr:row>26</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>16</xdr:col>
-          <xdr:colOff>228600</xdr:colOff>
-          <xdr:row>26</xdr:row>
-          <xdr:rowOff>53340</xdr:rowOff>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>27</xdr:row>
+          <xdr:rowOff>66675</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2462,14 +2461,14 @@
         <xdr:from>
           <xdr:col>16</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>26</xdr:row>
+          <xdr:row>27</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>16</xdr:col>
-          <xdr:colOff>228600</xdr:colOff>
-          <xdr:row>27</xdr:row>
-          <xdr:rowOff>53340</xdr:rowOff>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>28</xdr:row>
+          <xdr:rowOff>66675</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2512,14 +2511,14 @@
         <xdr:from>
           <xdr:col>16</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>27</xdr:row>
+          <xdr:row>28</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>16</xdr:col>
-          <xdr:colOff>228600</xdr:colOff>
-          <xdr:row>28</xdr:row>
-          <xdr:rowOff>60960</xdr:rowOff>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>29</xdr:row>
+          <xdr:rowOff>76200</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2562,14 +2561,14 @@
         <xdr:from>
           <xdr:col>16</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>28</xdr:row>
+          <xdr:row>29</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>16</xdr:col>
-          <xdr:colOff>228600</xdr:colOff>
-          <xdr:row>29</xdr:row>
-          <xdr:rowOff>60960</xdr:rowOff>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>30</xdr:row>
+          <xdr:rowOff>76200</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2612,14 +2611,14 @@
         <xdr:from>
           <xdr:col>16</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>29</xdr:row>
+          <xdr:row>30</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>16</xdr:col>
-          <xdr:colOff>228600</xdr:colOff>
-          <xdr:row>30</xdr:row>
-          <xdr:rowOff>60960</xdr:rowOff>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>31</xdr:row>
+          <xdr:rowOff>76200</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2662,14 +2661,14 @@
         <xdr:from>
           <xdr:col>16</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>30</xdr:row>
+          <xdr:row>31</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>16</xdr:col>
-          <xdr:colOff>228600</xdr:colOff>
-          <xdr:row>31</xdr:row>
-          <xdr:rowOff>60960</xdr:rowOff>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>32</xdr:row>
+          <xdr:rowOff>76200</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2712,14 +2711,14 @@
         <xdr:from>
           <xdr:col>16</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>31</xdr:row>
+          <xdr:row>32</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>16</xdr:col>
-          <xdr:colOff>228600</xdr:colOff>
-          <xdr:row>32</xdr:row>
-          <xdr:rowOff>53340</xdr:rowOff>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>33</xdr:row>
+          <xdr:rowOff>66675</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2762,14 +2761,14 @@
         <xdr:from>
           <xdr:col>16</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>32</xdr:row>
+          <xdr:row>33</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>16</xdr:col>
-          <xdr:colOff>228600</xdr:colOff>
-          <xdr:row>33</xdr:row>
-          <xdr:rowOff>60960</xdr:rowOff>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>34</xdr:row>
+          <xdr:rowOff>76200</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2812,14 +2811,14 @@
         <xdr:from>
           <xdr:col>16</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>33</xdr:row>
+          <xdr:row>34</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>16</xdr:col>
-          <xdr:colOff>228600</xdr:colOff>
-          <xdr:row>34</xdr:row>
-          <xdr:rowOff>60960</xdr:rowOff>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>35</xdr:row>
+          <xdr:rowOff>76200</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2862,14 +2861,14 @@
         <xdr:from>
           <xdr:col>16</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>34</xdr:row>
+          <xdr:row>35</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>16</xdr:col>
-          <xdr:colOff>228600</xdr:colOff>
-          <xdr:row>35</xdr:row>
-          <xdr:rowOff>53340</xdr:rowOff>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>36</xdr:row>
+          <xdr:rowOff>66675</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2912,14 +2911,14 @@
         <xdr:from>
           <xdr:col>16</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>16</xdr:col>
-          <xdr:colOff>228600</xdr:colOff>
-          <xdr:row>36</xdr:row>
-          <xdr:rowOff>53340</xdr:rowOff>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>37</xdr:row>
+          <xdr:rowOff>66675</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2962,14 +2961,14 @@
         <xdr:from>
           <xdr:col>16</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>36</xdr:row>
+          <xdr:row>37</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>16</xdr:col>
-          <xdr:colOff>228600</xdr:colOff>
-          <xdr:row>37</xdr:row>
-          <xdr:rowOff>60960</xdr:rowOff>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>38</xdr:row>
+          <xdr:rowOff>76200</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3012,14 +3011,14 @@
         <xdr:from>
           <xdr:col>16</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>37</xdr:row>
+          <xdr:row>38</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>16</xdr:col>
-          <xdr:colOff>228600</xdr:colOff>
-          <xdr:row>38</xdr:row>
-          <xdr:rowOff>60960</xdr:rowOff>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>39</xdr:row>
+          <xdr:rowOff>76200</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3062,14 +3061,14 @@
         <xdr:from>
           <xdr:col>16</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>38</xdr:row>
+          <xdr:row>39</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>16</xdr:col>
-          <xdr:colOff>228600</xdr:colOff>
-          <xdr:row>39</xdr:row>
-          <xdr:rowOff>60960</xdr:rowOff>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>40</xdr:row>
+          <xdr:rowOff>76200</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3112,14 +3111,14 @@
         <xdr:from>
           <xdr:col>16</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>39</xdr:row>
+          <xdr:row>40</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>16</xdr:col>
-          <xdr:colOff>228600</xdr:colOff>
-          <xdr:row>40</xdr:row>
-          <xdr:rowOff>60960</xdr:rowOff>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>41</xdr:row>
+          <xdr:rowOff>76200</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3162,14 +3161,14 @@
         <xdr:from>
           <xdr:col>16</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>40</xdr:row>
+          <xdr:row>41</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>16</xdr:col>
-          <xdr:colOff>228600</xdr:colOff>
-          <xdr:row>41</xdr:row>
-          <xdr:rowOff>60960</xdr:rowOff>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>42</xdr:row>
+          <xdr:rowOff>76200</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3212,14 +3211,14 @@
         <xdr:from>
           <xdr:col>16</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>41</xdr:row>
+          <xdr:row>42</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>16</xdr:col>
-          <xdr:colOff>228600</xdr:colOff>
-          <xdr:row>42</xdr:row>
-          <xdr:rowOff>60960</xdr:rowOff>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>43</xdr:row>
+          <xdr:rowOff>76200</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3262,14 +3261,14 @@
         <xdr:from>
           <xdr:col>16</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>42</xdr:row>
+          <xdr:row>43</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>16</xdr:col>
-          <xdr:colOff>228600</xdr:colOff>
-          <xdr:row>43</xdr:row>
-          <xdr:rowOff>60960</xdr:rowOff>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>44</xdr:row>
+          <xdr:rowOff>76200</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3312,14 +3311,14 @@
         <xdr:from>
           <xdr:col>16</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>43</xdr:row>
+          <xdr:row>44</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>16</xdr:col>
-          <xdr:colOff>228600</xdr:colOff>
-          <xdr:row>44</xdr:row>
-          <xdr:rowOff>60960</xdr:rowOff>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>45</xdr:row>
+          <xdr:rowOff>76200</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3362,14 +3361,14 @@
         <xdr:from>
           <xdr:col>16</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>44</xdr:row>
+          <xdr:row>45</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>16</xdr:col>
-          <xdr:colOff>228600</xdr:colOff>
-          <xdr:row>45</xdr:row>
-          <xdr:rowOff>60960</xdr:rowOff>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>46</xdr:row>
+          <xdr:rowOff>76200</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3412,14 +3411,14 @@
         <xdr:from>
           <xdr:col>16</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>45</xdr:row>
+          <xdr:row>46</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>16</xdr:col>
-          <xdr:colOff>228600</xdr:colOff>
-          <xdr:row>46</xdr:row>
-          <xdr:rowOff>60960</xdr:rowOff>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>47</xdr:row>
+          <xdr:rowOff>76200</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3462,14 +3461,14 @@
         <xdr:from>
           <xdr:col>16</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>46</xdr:row>
+          <xdr:row>47</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>16</xdr:col>
-          <xdr:colOff>228600</xdr:colOff>
-          <xdr:row>47</xdr:row>
-          <xdr:rowOff>60960</xdr:rowOff>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>48</xdr:row>
+          <xdr:rowOff>76200</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3512,14 +3511,14 @@
         <xdr:from>
           <xdr:col>16</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>47</xdr:row>
+          <xdr:row>48</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>16</xdr:col>
-          <xdr:colOff>228600</xdr:colOff>
-          <xdr:row>48</xdr:row>
-          <xdr:rowOff>60960</xdr:rowOff>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>49</xdr:row>
+          <xdr:rowOff>76200</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3562,14 +3561,14 @@
         <xdr:from>
           <xdr:col>16</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>48</xdr:row>
+          <xdr:row>49</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>16</xdr:col>
-          <xdr:colOff>228600</xdr:colOff>
-          <xdr:row>49</xdr:row>
-          <xdr:rowOff>60960</xdr:rowOff>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>50</xdr:row>
+          <xdr:rowOff>76200</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3612,14 +3611,14 @@
         <xdr:from>
           <xdr:col>16</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>49</xdr:row>
+          <xdr:row>50</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>16</xdr:col>
-          <xdr:colOff>228600</xdr:colOff>
-          <xdr:row>50</xdr:row>
-          <xdr:rowOff>60960</xdr:rowOff>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>51</xdr:row>
+          <xdr:rowOff>76200</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3662,14 +3661,14 @@
         <xdr:from>
           <xdr:col>16</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>50</xdr:row>
+          <xdr:row>51</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>16</xdr:col>
-          <xdr:colOff>228600</xdr:colOff>
-          <xdr:row>51</xdr:row>
-          <xdr:rowOff>60960</xdr:rowOff>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>52</xdr:row>
+          <xdr:rowOff>76200</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3712,14 +3711,14 @@
         <xdr:from>
           <xdr:col>16</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>51</xdr:row>
+          <xdr:row>52</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>16</xdr:col>
-          <xdr:colOff>228600</xdr:colOff>
-          <xdr:row>52</xdr:row>
-          <xdr:rowOff>60960</xdr:rowOff>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>53</xdr:row>
+          <xdr:rowOff>76200</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3762,14 +3761,14 @@
         <xdr:from>
           <xdr:col>16</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>52</xdr:row>
+          <xdr:row>53</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>16</xdr:col>
-          <xdr:colOff>228600</xdr:colOff>
-          <xdr:row>53</xdr:row>
-          <xdr:rowOff>60960</xdr:rowOff>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>54</xdr:row>
+          <xdr:rowOff>76200</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3812,14 +3811,14 @@
         <xdr:from>
           <xdr:col>16</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>53</xdr:row>
+          <xdr:row>54</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>16</xdr:col>
-          <xdr:colOff>228600</xdr:colOff>
-          <xdr:row>54</xdr:row>
-          <xdr:rowOff>60960</xdr:rowOff>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>55</xdr:row>
+          <xdr:rowOff>76200</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3862,14 +3861,14 @@
         <xdr:from>
           <xdr:col>16</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>54</xdr:row>
+          <xdr:row>55</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>16</xdr:col>
-          <xdr:colOff>228600</xdr:colOff>
-          <xdr:row>55</xdr:row>
-          <xdr:rowOff>60960</xdr:rowOff>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>56</xdr:row>
+          <xdr:rowOff>76200</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3912,14 +3911,14 @@
         <xdr:from>
           <xdr:col>16</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>55</xdr:row>
+          <xdr:row>56</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>16</xdr:col>
-          <xdr:colOff>228600</xdr:colOff>
-          <xdr:row>56</xdr:row>
-          <xdr:rowOff>60960</xdr:rowOff>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>57</xdr:row>
+          <xdr:rowOff>76200</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3962,14 +3961,14 @@
         <xdr:from>
           <xdr:col>16</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>56</xdr:row>
+          <xdr:row>57</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>16</xdr:col>
-          <xdr:colOff>228600</xdr:colOff>
-          <xdr:row>57</xdr:row>
-          <xdr:rowOff>53340</xdr:rowOff>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>58</xdr:row>
+          <xdr:rowOff>66675</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4010,9 +4009,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4050,7 +4049,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -4156,7 +4155,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4298,7 +4297,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -4307,2466 +4306,2022 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:P98"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:P99"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="3.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="G1" s="9" t="s">
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="G1" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3" t="s">
+      <c r="G2" t="s">
         <v>0</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" t="s">
         <v>1</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" t="s">
         <v>2</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" t="s">
         <v>3</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3">
         <v>2</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3">
+      <c r="D3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3">
         <v>1</v>
       </c>
-      <c r="H3" s="3" t="str">
+      <c r="H3" t="str">
         <f>B3</f>
         <v>RecordType</v>
       </c>
-      <c r="I3" s="3">
+      <c r="I3">
         <v>2</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="6">
+      <c r="J3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4">
         <v>2</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4" t="s">
+        <v>114</v>
+      </c>
+      <c r="I4">
+        <v>2</v>
+      </c>
+      <c r="J4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="5">
+        <v>2</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C5" s="5">
         <v>1</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="6" t="s">
+      <c r="D5" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="6"/>
-      <c r="G4" s="4">
-        <v>6</v>
-      </c>
-      <c r="H4" s="4" t="s">
+      <c r="G5" s="3">
+        <v>6</v>
+      </c>
+      <c r="H5" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="I4" s="4">
+      <c r="I5" s="3">
         <v>2</v>
       </c>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6" t="s">
+      <c r="K5" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A5" s="3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B6" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="3">
-        <v>6</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3">
+      <c r="C6">
+        <v>6</v>
+      </c>
+      <c r="D6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6">
         <v>3</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H6" t="s">
         <v>10</v>
       </c>
-      <c r="I5" s="3">
-        <v>6</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A6" s="3">
+      <c r="I6">
+        <v>6</v>
+      </c>
+      <c r="J6" t="s">
+        <v>6</v>
+      </c>
+      <c r="K6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7">
         <v>4</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B7" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C7">
         <v>4</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3">
-        <v>7</v>
-      </c>
-      <c r="H6" s="3" t="s">
+      <c r="D7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" t="s">
+        <v>7</v>
+      </c>
+      <c r="G7">
+        <v>7</v>
+      </c>
+      <c r="H7" t="s">
         <v>11</v>
       </c>
-      <c r="I6" s="3">
-        <v>6</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A7" s="3">
+      <c r="I7">
+        <v>6</v>
+      </c>
+      <c r="J7" t="s">
+        <v>6</v>
+      </c>
+      <c r="K7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8">
         <v>5</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B8" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="3">
-        <v>6</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3">
+      <c r="C8">
+        <v>6</v>
+      </c>
+      <c r="D8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" t="s">
+        <v>7</v>
+      </c>
+      <c r="G8">
         <v>8</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="H8" t="s">
         <v>12</v>
       </c>
-      <c r="I7" s="3">
+      <c r="I8">
         <v>15</v>
       </c>
-      <c r="J7" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A8" s="3">
-        <v>6</v>
-      </c>
-      <c r="B8" s="3" t="s">
+      <c r="J8" t="s">
+        <v>6</v>
+      </c>
+      <c r="K8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C9">
         <v>3</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D9" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E9" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A9" s="3">
-        <v>7</v>
-      </c>
-      <c r="B9" s="3" t="s">
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C10">
         <v>2</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D10" t="s">
         <v>14</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="3">
+      <c r="E10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11">
         <v>8</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B11" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C11">
         <v>2</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D11" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="6">
+      <c r="E11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" s="5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="5">
         <v>9</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B12" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="6">
-        <v>6</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" s="6"/>
-      <c r="G11" s="4">
+      <c r="C12" s="5">
+        <v>6</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="G12" s="3">
         <v>13</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="H12" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="I11" s="4">
+      <c r="I12" s="3">
         <v>15</v>
       </c>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="6">
+      <c r="K12" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" s="5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="5">
         <v>10</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B13" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="6">
-        <v>6</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E12" s="6" t="s">
+      <c r="C13" s="5">
+        <v>6</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E13" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F12" s="6"/>
-      <c r="G12" s="4">
+      <c r="G13" s="3">
         <v>14</v>
       </c>
-      <c r="H12" s="4" t="s">
+      <c r="H13" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="I12" s="4">
+      <c r="I13" s="3">
         <v>20</v>
       </c>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="6">
+      <c r="K13" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" s="5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="5">
         <v>11</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B14" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C14" s="5">
         <v>4</v>
       </c>
-      <c r="D13" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" s="6"/>
-      <c r="G13" s="4">
+      <c r="D14" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="G14" s="3">
         <v>19</v>
       </c>
-      <c r="H13" s="4" t="s">
+      <c r="H14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="I13" s="4">
+      <c r="I14" s="3">
         <v>4</v>
       </c>
-      <c r="J13" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="K13" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="6">
+      <c r="J14" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" s="5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="5">
         <v>12</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B15" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C15" s="5">
         <v>2</v>
       </c>
-      <c r="D14" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E14" s="6" t="s">
+      <c r="D15" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E15" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F14" s="6"/>
-      <c r="G14" s="4">
+      <c r="G15" s="3">
         <v>18</v>
       </c>
-      <c r="H14" s="4" t="s">
+      <c r="H15" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="I14" s="4">
+      <c r="I15" s="3">
         <v>2</v>
       </c>
-      <c r="J14" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="K14" s="6" t="s">
+      <c r="J15" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="K15" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:16" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="6">
+    <row r="16" spans="1:16" s="5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="5">
         <v>13</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B16" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C16" s="5">
         <v>2</v>
       </c>
-      <c r="D15" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E15" s="6" t="s">
+      <c r="D16" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E16" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F15" s="6"/>
-      <c r="G15" s="4">
+      <c r="G16" s="3">
         <v>17</v>
       </c>
-      <c r="H15" s="4" t="s">
+      <c r="H16" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="I15" s="4">
+      <c r="I16" s="3">
         <v>2</v>
       </c>
-      <c r="J15" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="K15" s="6" t="s">
+      <c r="J16" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="K16" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:16" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="8">
+    <row r="17" spans="1:11" s="5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="9">
         <v>14</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B17" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="8">
+      <c r="C17" s="9">
         <v>4</v>
       </c>
-      <c r="D16" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" s="6"/>
-      <c r="G16" s="4">
+      <c r="D17" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G17" s="3">
         <v>20</v>
       </c>
-      <c r="H16" s="4" t="s">
+      <c r="H17" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="I16" s="4">
+      <c r="I17" s="3">
         <v>2</v>
       </c>
-      <c r="J16" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="K16" s="6" t="s">
+      <c r="J17" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="K17" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="4">
+    <row r="18" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="9"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="G18" s="3">
         <v>21</v>
       </c>
-      <c r="H17" s="4" t="s">
+      <c r="H18" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="I17" s="4">
+      <c r="I18" s="3">
         <v>2</v>
       </c>
-      <c r="J17" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="K17" s="6" t="s">
+      <c r="J18" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="K18" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:11" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="6">
+    <row r="19" spans="1:11" s="5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="5">
         <v>15</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B19" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C19" s="5">
         <v>4</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D19" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E18" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
-    </row>
-    <row r="19" spans="1:11" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="8">
+      <c r="E19" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" s="5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="9">
         <v>16</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B20" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C19" s="8">
+      <c r="C20" s="9">
         <v>3</v>
       </c>
-      <c r="D19" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="E19" s="8" t="s">
+      <c r="D20" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E20" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F19" s="6"/>
-      <c r="G19" s="4">
+      <c r="G20" s="3">
         <v>24</v>
       </c>
-      <c r="H19" s="4" t="s">
+      <c r="H20" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="I19" s="4">
+      <c r="I20" s="3">
         <v>5</v>
       </c>
-      <c r="J19" s="6"/>
-      <c r="K19" s="6" t="s">
+      <c r="K20" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="20" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="4">
+    <row r="21" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="9"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+      <c r="G21" s="3">
         <v>25</v>
       </c>
-      <c r="H20" s="4" t="s">
+      <c r="H21" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="I20" s="4">
+      <c r="I21" s="3">
         <v>8</v>
       </c>
-      <c r="J20" s="6"/>
-      <c r="K20" s="6" t="s">
+      <c r="K21" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:11" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="6">
+    <row r="22" spans="1:11" s="5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="5">
         <v>17</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B22" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C21" s="6">
+      <c r="C22" s="5">
         <v>2</v>
       </c>
-      <c r="D21" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6" t="s">
+      <c r="D22" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="H22" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="I21" s="5">
+      <c r="I22" s="4">
         <v>1</v>
       </c>
-      <c r="J21" s="6"/>
-      <c r="K21" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="6">
+      <c r="K22" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" s="5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="5">
         <v>18</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B23" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C22" s="6">
+      <c r="C23" s="5">
         <v>8</v>
       </c>
-      <c r="D22" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E22" s="6" t="s">
+      <c r="D23" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E23" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F22" s="6"/>
-      <c r="G22" s="4">
+      <c r="G23" s="3">
         <v>22</v>
       </c>
-      <c r="H22" s="4" t="s">
+      <c r="H23" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="I22" s="4">
+      <c r="I23" s="3">
         <v>20</v>
       </c>
-      <c r="J22" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="K22" s="6" t="s">
+      <c r="J23" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="K23" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="23" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="6">
+    <row r="24" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="5">
         <v>19</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B24" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C23" s="6">
+      <c r="C24" s="5">
         <v>9</v>
       </c>
-      <c r="D23" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E23" s="6" t="s">
+      <c r="D24" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E24" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F23" s="6"/>
-      <c r="G23" s="4">
+      <c r="G24" s="3">
         <v>23</v>
       </c>
-      <c r="H23" s="4" t="s">
+      <c r="H24" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="I23" s="4">
+      <c r="I24" s="3">
         <v>20</v>
       </c>
-      <c r="J23" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="K23" s="6" t="s">
+      <c r="J24" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="K24" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="24" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="6">
+    <row r="25" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="5">
         <v>20</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B25" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C24" s="6">
+      <c r="C25" s="5">
         <v>8</v>
       </c>
-      <c r="D24" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E24" s="6" t="s">
+      <c r="D25" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E25" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
-      <c r="J24" s="6"/>
-      <c r="K24" s="6"/>
-    </row>
-    <row r="25" spans="1:11" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="6">
+    </row>
+    <row r="26" spans="1:11" s="5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="5">
         <v>21</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B26" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C25" s="6">
+      <c r="C26" s="5">
         <v>9</v>
       </c>
-      <c r="D25" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E25" s="6" t="s">
+      <c r="D26" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E26" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="6"/>
-      <c r="I25" s="6"/>
-      <c r="J25" s="6"/>
-      <c r="K25" s="6"/>
-    </row>
-    <row r="26" spans="1:11" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="6">
+    </row>
+    <row r="27" spans="1:11" s="5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="5">
         <v>22</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B27" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C26" s="6">
+      <c r="C27" s="5">
         <v>4</v>
       </c>
-      <c r="D26" s="6" t="s">
+      <c r="D27" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E26" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F26" s="6"/>
-      <c r="G26" s="4">
+      <c r="E27" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="G27" s="3">
         <v>52</v>
       </c>
-      <c r="H26" s="4" t="s">
+      <c r="H27" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="I26" s="4">
+      <c r="I27" s="3">
         <v>10</v>
       </c>
-      <c r="J26" s="6"/>
-      <c r="K26" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="6">
+      <c r="K27" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" s="5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="5">
         <v>23</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B28" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C27" s="6">
+      <c r="C28" s="5">
         <v>4</v>
       </c>
-      <c r="D27" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E27" s="6" t="s">
+      <c r="D28" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E28" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F27" s="6"/>
-      <c r="G27" s="4">
+      <c r="G28" s="3">
         <v>43</v>
       </c>
-      <c r="H27" s="4" t="s">
+      <c r="H28" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="I27" s="4">
+      <c r="I28" s="3">
         <v>3</v>
       </c>
-      <c r="J27" s="6"/>
-      <c r="K27" s="6" t="s">
+      <c r="K28" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="28" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="6">
+    <row r="29" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="5">
         <v>24</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B29" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C28" s="6">
+      <c r="C29" s="5">
         <v>1</v>
       </c>
-      <c r="D28" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F28" s="6"/>
-      <c r="G28" s="4">
+      <c r="D29" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="G29" s="3">
         <v>15</v>
       </c>
-      <c r="H28" s="4" t="s">
+      <c r="H29" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="I28" s="4">
+      <c r="I29" s="3">
         <v>2</v>
       </c>
-      <c r="J28" s="6"/>
-      <c r="K28" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="6">
+      <c r="K29" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="5">
         <v>25</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B30" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C29" s="6">
+      <c r="C30" s="5">
         <v>8</v>
       </c>
-      <c r="D29" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F29" s="6"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="6"/>
-      <c r="I29" s="6"/>
-      <c r="J29" s="6"/>
-      <c r="K29" s="6"/>
-    </row>
-    <row r="30" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="6">
+      <c r="D30" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="5">
         <v>26</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B31" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C30" s="6">
+      <c r="C31" s="5">
         <v>1</v>
       </c>
-      <c r="D30" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F30" s="6"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="6"/>
-      <c r="I30" s="6"/>
-      <c r="J30" s="6"/>
-      <c r="K30" s="6"/>
-    </row>
-    <row r="31" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="6">
+      <c r="D31" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="5">
         <v>27</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B32" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C31" s="6">
+      <c r="C32" s="5">
         <v>1</v>
       </c>
-      <c r="D31" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E31" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="6"/>
-      <c r="I31" s="6"/>
-      <c r="J31" s="6"/>
-      <c r="K31" s="6"/>
-    </row>
-    <row r="32" spans="1:11" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="6">
+      <c r="D32" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" s="5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="5">
         <v>28</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="B33" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C32" s="6">
+      <c r="C33" s="5">
         <v>2</v>
       </c>
-      <c r="D32" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="6"/>
-      <c r="I32" s="6"/>
-      <c r="J32" s="6"/>
-      <c r="K32" s="6"/>
-    </row>
-    <row r="33" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="6">
+      <c r="D33" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="5">
         <v>29</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="B34" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C33" s="6">
+      <c r="C34" s="5">
         <v>4</v>
       </c>
-      <c r="D33" s="6" t="s">
+      <c r="D34" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E33" s="6" t="s">
+      <c r="E34" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="F33" s="6"/>
-      <c r="G33" s="4">
+      <c r="G34" s="3">
         <v>29</v>
       </c>
-      <c r="H33" s="4" t="s">
+      <c r="H34" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="I33" s="4">
-        <v>6</v>
-      </c>
-      <c r="J33" s="6"/>
-      <c r="K33" s="6" t="s">
+      <c r="I34" s="3">
+        <v>6</v>
+      </c>
+      <c r="K34" s="5" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="34" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="6">
+    <row r="35" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="5">
         <v>30</v>
       </c>
-      <c r="B34" s="6" t="s">
+      <c r="B35" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C34" s="6">
+      <c r="C35" s="5">
         <v>2</v>
       </c>
-      <c r="D34" s="6" t="s">
+      <c r="D35" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E34" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F34" s="6"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="6"/>
-      <c r="I34" s="6"/>
-      <c r="J34" s="6"/>
-      <c r="K34" s="6"/>
-    </row>
-    <row r="35" spans="1:11" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="6">
+      <c r="E35" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" s="5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="5">
         <v>31</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="B36" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C35" s="6">
+      <c r="C36" s="5">
         <v>2</v>
       </c>
-      <c r="D35" s="6" t="s">
+      <c r="D36" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E35" s="6" t="s">
+      <c r="E36" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F35" s="6"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="6"/>
-      <c r="I35" s="6"/>
-      <c r="J35" s="6"/>
-      <c r="K35" s="6"/>
-    </row>
-    <row r="36" spans="1:11" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="6">
+    </row>
+    <row r="37" spans="1:11" s="5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="5">
         <v>32</v>
       </c>
-      <c r="B36" s="6" t="s">
+      <c r="B37" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C36" s="6">
+      <c r="C37" s="5">
         <v>5</v>
       </c>
-      <c r="D36" s="6" t="s">
+      <c r="D37" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E36" s="6" t="s">
+      <c r="E37" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="F36" s="6"/>
-      <c r="G36" s="4">
+      <c r="G37" s="3">
         <v>26</v>
       </c>
-      <c r="H36" s="4" t="s">
+      <c r="H37" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="I36" s="4">
+      <c r="I37" s="3">
         <v>5</v>
       </c>
-      <c r="J36" s="6"/>
-      <c r="K36" s="6" t="s">
+      <c r="K37" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="37" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="6">
+    <row r="38" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="5">
         <v>33</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B38" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C37" s="6">
+      <c r="C38" s="5">
         <v>4</v>
       </c>
-      <c r="D37" s="6" t="s">
+      <c r="D38" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E37" s="6" t="s">
+      <c r="E38" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F37" s="6"/>
-      <c r="G37" s="4">
+      <c r="G38" s="3">
         <v>28</v>
       </c>
-      <c r="H37" s="4" t="s">
+      <c r="H38" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="I37" s="4">
-        <v>7</v>
-      </c>
-      <c r="J37" s="6"/>
-      <c r="K37" s="6" t="s">
+      <c r="I38" s="3">
+        <v>7</v>
+      </c>
+      <c r="K38" s="5" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="38" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="6">
+    <row r="39" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="5">
         <v>34</v>
       </c>
-      <c r="B38" s="6" t="s">
+      <c r="B39" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C38" s="6">
+      <c r="C39" s="5">
         <v>2</v>
       </c>
-      <c r="D38" s="6" t="s">
+      <c r="D39" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E38" s="6" t="s">
+      <c r="E39" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F38" s="6"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="6"/>
-      <c r="I38" s="6"/>
-      <c r="J38" s="6"/>
-      <c r="K38" s="6"/>
-    </row>
-    <row r="39" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="6">
+    </row>
+    <row r="40" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="5">
         <v>35</v>
       </c>
-      <c r="B39" s="6" t="s">
+      <c r="B40" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C39" s="6">
+      <c r="C40" s="5">
         <v>2</v>
       </c>
-      <c r="D39" s="6" t="s">
+      <c r="D40" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E39" s="6" t="s">
+      <c r="E40" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F39" s="6"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="6"/>
-      <c r="I39" s="6"/>
-      <c r="J39" s="6"/>
-      <c r="K39" s="6"/>
-    </row>
-    <row r="40" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="6">
+    </row>
+    <row r="41" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="5">
         <v>36</v>
       </c>
-      <c r="B40" s="6" t="s">
+      <c r="B41" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C40" s="6">
+      <c r="C41" s="5">
         <v>4</v>
       </c>
-      <c r="D40" s="6" t="s">
+      <c r="D41" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E40" s="6" t="s">
+      <c r="E41" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="F40" s="6"/>
-      <c r="G40" s="6"/>
-      <c r="H40" s="6"/>
-      <c r="I40" s="6"/>
-      <c r="J40" s="6"/>
-      <c r="K40" s="6"/>
-    </row>
-    <row r="41" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="6">
+    </row>
+    <row r="42" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="5">
         <v>37</v>
       </c>
-      <c r="B41" s="6" t="s">
+      <c r="B42" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C41" s="6">
+      <c r="C42" s="5">
         <v>4</v>
       </c>
-      <c r="D41" s="6" t="s">
+      <c r="D42" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E41" s="6" t="s">
+      <c r="E42" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F41" s="6"/>
-      <c r="G41" s="6"/>
-      <c r="H41" s="6"/>
-      <c r="I41" s="6"/>
-      <c r="J41" s="6"/>
-      <c r="K41" s="6"/>
-    </row>
-    <row r="42" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="6">
+    </row>
+    <row r="43" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="5">
         <v>38</v>
       </c>
-      <c r="B42" s="6" t="s">
+      <c r="B43" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C42" s="6">
+      <c r="C43" s="5">
         <v>5</v>
       </c>
-      <c r="D42" s="6" t="s">
+      <c r="D43" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E42" s="6" t="s">
+      <c r="E43" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="F42" s="6"/>
-      <c r="G42" s="6"/>
-      <c r="H42" s="6"/>
-      <c r="I42" s="6"/>
-      <c r="J42" s="6"/>
-      <c r="K42" s="6"/>
-    </row>
-    <row r="43" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="6">
+    </row>
+    <row r="44" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="5">
         <v>39</v>
       </c>
-      <c r="B43" s="6" t="s">
+      <c r="B44" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C43" s="6">
+      <c r="C44" s="5">
         <v>4</v>
       </c>
-      <c r="D43" s="6" t="s">
+      <c r="D44" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E43" s="6" t="s">
+      <c r="E44" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="F43" s="6"/>
-      <c r="G43" s="6"/>
-      <c r="H43" s="6"/>
-      <c r="I43" s="6"/>
-      <c r="J43" s="6"/>
-      <c r="K43" s="6"/>
-    </row>
-    <row r="44" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="6">
+    </row>
+    <row r="45" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="5">
         <v>40</v>
       </c>
-      <c r="B44" s="6" t="s">
+      <c r="B45" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C44" s="6">
+      <c r="C45" s="5">
         <v>4</v>
       </c>
-      <c r="D44" s="6" t="s">
+      <c r="D45" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E44" s="6" t="s">
+      <c r="E45" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F44" s="6"/>
-      <c r="G44" s="6"/>
-      <c r="H44" s="6"/>
-      <c r="I44" s="6"/>
-      <c r="J44" s="6"/>
-      <c r="K44" s="6"/>
-    </row>
-    <row r="45" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="6">
+    </row>
+    <row r="46" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="5">
         <v>41</v>
       </c>
-      <c r="B45" s="6" t="s">
+      <c r="B46" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C45" s="6">
+      <c r="C46" s="5">
         <v>3</v>
       </c>
-      <c r="D45" s="6" t="s">
+      <c r="D46" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E45" s="6" t="s">
+      <c r="E46" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="F45" s="6"/>
-      <c r="G45" s="6"/>
-      <c r="H45" s="6"/>
-      <c r="I45" s="6"/>
-      <c r="J45" s="6"/>
-      <c r="K45" s="6"/>
-    </row>
-    <row r="46" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="6">
+    </row>
+    <row r="47" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="5">
         <v>42</v>
       </c>
-      <c r="B46" s="6" t="s">
+      <c r="B47" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C46" s="6">
+      <c r="C47" s="5">
         <v>4</v>
       </c>
-      <c r="D46" s="6" t="s">
+      <c r="D47" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E46" s="6" t="s">
+      <c r="E47" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F46" s="6"/>
-      <c r="G46" s="6"/>
-      <c r="H46" s="6"/>
-      <c r="I46" s="6"/>
-      <c r="J46" s="6"/>
-      <c r="K46" s="6"/>
-    </row>
-    <row r="47" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="6">
+    </row>
+    <row r="48" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="5">
         <v>43</v>
       </c>
-      <c r="B47" s="6" t="s">
+      <c r="B48" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C47" s="6">
+      <c r="C48" s="5">
         <v>3</v>
       </c>
-      <c r="D47" s="6" t="s">
+      <c r="D48" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E47" s="6" t="s">
+      <c r="E48" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F47" s="6"/>
-      <c r="G47" s="6"/>
-      <c r="H47" s="6"/>
-      <c r="I47" s="6"/>
-      <c r="J47" s="6"/>
-      <c r="K47" s="6"/>
-    </row>
-    <row r="48" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="6">
+    </row>
+    <row r="49" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="5">
         <v>44</v>
       </c>
-      <c r="B48" s="6" t="s">
+      <c r="B49" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C48" s="6">
+      <c r="C49" s="5">
         <v>3</v>
       </c>
-      <c r="D48" s="6" t="s">
+      <c r="D49" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E48" s="6" t="s">
+      <c r="E49" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="F48" s="6"/>
-      <c r="G48" s="6"/>
-      <c r="H48" s="6"/>
-      <c r="I48" s="6"/>
-      <c r="J48" s="6"/>
-      <c r="K48" s="6"/>
-    </row>
-    <row r="49" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="6">
+    </row>
+    <row r="50" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="5">
         <v>45</v>
       </c>
-      <c r="B49" s="6" t="s">
+      <c r="B50" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C49" s="6">
+      <c r="C50" s="5">
         <v>3</v>
       </c>
-      <c r="D49" s="6" t="s">
+      <c r="D50" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E49" s="6" t="s">
+      <c r="E50" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="F49" s="6"/>
-      <c r="G49" s="6"/>
-      <c r="H49" s="6"/>
-      <c r="I49" s="6"/>
-      <c r="J49" s="6"/>
-      <c r="K49" s="6"/>
-    </row>
-    <row r="50" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="6">
+    </row>
+    <row r="51" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="5">
         <v>46</v>
       </c>
-      <c r="B50" s="6" t="s">
+      <c r="B51" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C50" s="6">
+      <c r="C51" s="5">
         <v>3</v>
       </c>
-      <c r="D50" s="6" t="s">
+      <c r="D51" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E50" s="6" t="s">
+      <c r="E51" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F50" s="6"/>
-      <c r="G50" s="6"/>
-      <c r="H50" s="6"/>
-      <c r="I50" s="6"/>
-      <c r="J50" s="6"/>
-      <c r="K50" s="6"/>
-    </row>
-    <row r="51" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="6">
+    </row>
+    <row r="52" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="5">
         <v>47</v>
       </c>
-      <c r="B51" s="6" t="s">
+      <c r="B52" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="C51" s="6">
+      <c r="C52" s="5">
         <v>4</v>
       </c>
-      <c r="D51" s="6" t="s">
+      <c r="D52" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E51" s="6" t="s">
+      <c r="E52" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="F51" s="6"/>
-      <c r="G51" s="6"/>
-      <c r="H51" s="6"/>
-      <c r="I51" s="6"/>
-      <c r="J51" s="6"/>
-      <c r="K51" s="6"/>
-    </row>
-    <row r="52" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="6">
+    </row>
+    <row r="53" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="5">
         <v>48</v>
       </c>
-      <c r="B52" s="6" t="s">
+      <c r="B53" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C52" s="6">
+      <c r="C53" s="5">
         <v>3</v>
       </c>
-      <c r="D52" s="6" t="s">
+      <c r="D53" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E52" s="6" t="s">
+      <c r="E53" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F52" s="6"/>
-      <c r="G52" s="6"/>
-      <c r="H52" s="6"/>
-      <c r="I52" s="6"/>
-      <c r="J52" s="6"/>
-      <c r="K52" s="6"/>
-    </row>
-    <row r="53" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="6">
+    </row>
+    <row r="54" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="5">
         <v>49</v>
       </c>
-      <c r="B53" s="6" t="s">
+      <c r="B54" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="C53" s="6">
+      <c r="C54" s="5">
         <v>4</v>
       </c>
-      <c r="D53" s="6" t="s">
+      <c r="D54" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E53" s="6" t="s">
+      <c r="E54" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="F53" s="6"/>
-      <c r="G53" s="6"/>
-      <c r="H53" s="6"/>
-      <c r="I53" s="6"/>
-      <c r="J53" s="6"/>
-      <c r="K53" s="6"/>
-    </row>
-    <row r="54" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="6">
+    </row>
+    <row r="55" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="5">
         <v>50</v>
       </c>
-      <c r="B54" s="6" t="s">
+      <c r="B55" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C54" s="6">
+      <c r="C55" s="5">
         <v>3</v>
       </c>
-      <c r="D54" s="6" t="s">
+      <c r="D55" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E54" s="6" t="s">
+      <c r="E55" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F54" s="6"/>
-      <c r="G54" s="6"/>
-      <c r="H54" s="6"/>
-      <c r="I54" s="6"/>
-      <c r="J54" s="6"/>
-      <c r="K54" s="6"/>
-    </row>
-    <row r="55" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="6">
+    </row>
+    <row r="56" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="5">
         <v>51</v>
       </c>
-      <c r="B55" s="6" t="s">
+      <c r="B56" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="C55" s="6">
+      <c r="C56" s="5">
         <v>3</v>
       </c>
-      <c r="D55" s="6" t="s">
+      <c r="D56" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E55" s="6" t="s">
+      <c r="E56" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F55" s="6"/>
-      <c r="G55" s="6"/>
-      <c r="H55" s="6"/>
-      <c r="I55" s="6"/>
-      <c r="J55" s="6"/>
-      <c r="K55" s="6"/>
-    </row>
-    <row r="56" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="6">
+    </row>
+    <row r="57" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="5">
         <v>52</v>
       </c>
-      <c r="B56" s="6" t="s">
+      <c r="B57" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C56" s="6">
+      <c r="C57" s="5">
         <v>3</v>
       </c>
-      <c r="D56" s="6" t="s">
+      <c r="D57" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E56" s="6" t="s">
+      <c r="E57" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F56" s="6"/>
-      <c r="G56" s="6"/>
-      <c r="H56" s="6"/>
-      <c r="I56" s="6"/>
-      <c r="J56" s="6"/>
-      <c r="K56" s="6"/>
-    </row>
-    <row r="57" spans="1:11" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="6">
+    </row>
+    <row r="58" spans="1:11" s="5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="5">
         <v>53</v>
       </c>
-      <c r="B57" s="6" t="s">
+      <c r="B58" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C57" s="6">
+      <c r="C58" s="5">
         <v>4</v>
       </c>
-      <c r="D57" s="6" t="s">
+      <c r="D58" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E57" s="6" t="s">
+      <c r="E58" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="F57" s="6"/>
-      <c r="G57" s="6"/>
-      <c r="H57" s="6"/>
-      <c r="I57" s="6"/>
-      <c r="J57" s="6"/>
-      <c r="K57" s="6"/>
-    </row>
-    <row r="58" spans="1:11" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="6">
+    </row>
+    <row r="59" spans="1:11" s="5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="5">
         <v>54</v>
       </c>
-      <c r="B58" s="6" t="s">
+      <c r="B59" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="C58" s="6">
+      <c r="C59" s="5">
         <v>4</v>
       </c>
-      <c r="D58" s="6" t="s">
+      <c r="D59" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E58" s="6" t="s">
+      <c r="E59" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="F58" s="6"/>
-      <c r="G58" s="4">
+      <c r="G59" s="3">
         <v>44</v>
       </c>
-      <c r="H58" s="4" t="s">
+      <c r="H59" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="I58" s="4">
+      <c r="I59" s="3">
         <v>4</v>
       </c>
-      <c r="J58" s="6"/>
-      <c r="K58" s="6" t="s">
+      <c r="K59" s="5" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="59" spans="1:11" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="6">
+    <row r="60" spans="1:11" s="5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="5">
         <v>55</v>
       </c>
-      <c r="B59" s="6" t="s">
+      <c r="B60" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C59" s="6">
+      <c r="C60" s="5">
         <v>4</v>
       </c>
-      <c r="D59" s="6" t="s">
+      <c r="D60" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E59" s="6" t="s">
+      <c r="E60" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="F59" s="6"/>
-      <c r="G59" s="4">
+      <c r="G60" s="3">
         <v>48</v>
       </c>
-      <c r="H59" s="4" t="s">
+      <c r="H60" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="I59" s="4">
+      <c r="I60" s="3">
         <v>4</v>
       </c>
-      <c r="J59" s="6"/>
-      <c r="K59" s="6" t="s">
+      <c r="K60" s="5" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="60" spans="1:11" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="6">
+    <row r="61" spans="1:11" s="5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="5">
         <v>56</v>
       </c>
-      <c r="B60" s="6" t="s">
+      <c r="B61" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="C60" s="6">
+      <c r="C61" s="5">
         <v>5</v>
       </c>
-      <c r="D60" s="6" t="s">
+      <c r="D61" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E60" s="6" t="s">
+      <c r="E61" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="F60" s="6"/>
-      <c r="G60" s="4">
+      <c r="G61" s="3">
         <v>49</v>
       </c>
-      <c r="H60" s="4" t="s">
+      <c r="H61" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="I60" s="4">
+      <c r="I61" s="3">
         <v>5</v>
       </c>
-      <c r="J60" s="6"/>
-      <c r="K60" s="6" t="s">
+      <c r="K61" s="5" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="61" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="6">
+    <row r="62" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="5">
         <v>57</v>
       </c>
-      <c r="B61" s="6" t="s">
+      <c r="B62" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="C61" s="6">
+      <c r="C62" s="5">
         <v>5</v>
       </c>
-      <c r="D61" s="6" t="s">
+      <c r="D62" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E61" s="6" t="s">
+      <c r="E62" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="F61" s="6"/>
-      <c r="G61" s="4">
+      <c r="G62" s="3">
         <v>51</v>
       </c>
-      <c r="H61" s="4" t="s">
+      <c r="H62" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="I61" s="4">
+      <c r="I62" s="3">
         <v>5</v>
       </c>
-      <c r="J61" s="6"/>
-      <c r="K61" s="6" t="s">
+      <c r="K62" s="5" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="62" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="6">
+    <row r="63" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="5">
         <v>58</v>
       </c>
-      <c r="B62" s="6" t="s">
+      <c r="B63" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="C62" s="6">
+      <c r="C63" s="5">
         <v>2</v>
       </c>
-      <c r="D62" s="6" t="s">
+      <c r="D63" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E62" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F62" s="6"/>
-      <c r="G62" s="6"/>
-      <c r="H62" s="6"/>
-      <c r="I62" s="6"/>
-      <c r="J62" s="6"/>
-      <c r="K62" s="6"/>
-    </row>
-    <row r="63" spans="1:11" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="6">
+      <c r="E63" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" s="5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="5">
         <v>59</v>
       </c>
-      <c r="B63" s="6" t="s">
+      <c r="B64" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="C63" s="6">
+      <c r="C64" s="5">
         <v>4</v>
       </c>
-      <c r="D63" s="6" t="s">
+      <c r="D64" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E63" s="6" t="s">
+      <c r="E64" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F63" s="6"/>
-      <c r="G63" s="6"/>
-      <c r="H63" s="6"/>
-      <c r="I63" s="6"/>
-      <c r="J63" s="6"/>
-      <c r="K63" s="6"/>
-    </row>
-    <row r="64" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="6">
+    </row>
+    <row r="65" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="5">
         <v>60</v>
       </c>
-      <c r="B64" s="6" t="s">
+      <c r="B65" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="C64" s="6">
+      <c r="C65" s="5">
         <v>4</v>
       </c>
-      <c r="D64" s="6" t="s">
+      <c r="D65" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E64" s="6" t="s">
+      <c r="E65" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F64" s="6"/>
-      <c r="G64" s="4">
+      <c r="G65" s="3">
         <v>12</v>
       </c>
-      <c r="H64" s="4" t="s">
+      <c r="H65" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="I64" s="4">
-        <v>6</v>
-      </c>
-      <c r="J64" s="6"/>
-      <c r="K64" s="6" t="s">
+      <c r="I65" s="3">
+        <v>6</v>
+      </c>
+      <c r="K65" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="65" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="6">
+    <row r="66" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="5">
         <v>61</v>
       </c>
-      <c r="B65" s="6" t="s">
+      <c r="B66" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C65" s="6">
-        <v>6</v>
-      </c>
-      <c r="D65" s="6" t="s">
+      <c r="C66" s="5">
+        <v>6</v>
+      </c>
+      <c r="D66" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E65" s="6" t="s">
+      <c r="E66" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="F65" s="6"/>
-      <c r="G65" s="6"/>
-      <c r="H65" s="6"/>
-      <c r="I65" s="6"/>
-      <c r="J65" s="6"/>
-      <c r="K65" s="6"/>
-    </row>
-    <row r="66" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="6">
+    </row>
+    <row r="67" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="5">
         <v>62</v>
       </c>
-      <c r="B66" s="6" t="s">
+      <c r="B67" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="C66" s="6">
-        <v>6</v>
-      </c>
-      <c r="D66" s="6" t="s">
+      <c r="C67" s="5">
+        <v>6</v>
+      </c>
+      <c r="D67" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E66" s="6" t="s">
+      <c r="E67" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F66" s="6"/>
-      <c r="G66" s="6"/>
-      <c r="H66" s="6"/>
-      <c r="I66" s="6"/>
-      <c r="J66" s="6"/>
-      <c r="K66" s="6"/>
-    </row>
-    <row r="67" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="6">
+    </row>
+    <row r="68" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="5">
         <v>63</v>
       </c>
-      <c r="B67" s="6" t="s">
+      <c r="B68" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="C67" s="6">
+      <c r="C68" s="5">
         <v>4</v>
       </c>
-      <c r="D67" s="6" t="s">
+      <c r="D68" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E67" s="6" t="s">
+      <c r="E68" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F67" s="6"/>
-      <c r="G67" s="6"/>
-      <c r="H67" s="6"/>
-      <c r="I67" s="6"/>
-      <c r="J67" s="6"/>
-      <c r="K67" s="6"/>
-    </row>
-    <row r="68" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="6">
+    </row>
+    <row r="69" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="5">
         <v>64</v>
       </c>
-      <c r="B68" s="6" t="s">
+      <c r="B69" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="C68" s="6">
+      <c r="C69" s="5">
         <v>4</v>
       </c>
-      <c r="D68" s="6" t="s">
+      <c r="D69" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E68" s="6" t="s">
+      <c r="E69" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="F68" s="6"/>
-      <c r="G68" s="6"/>
-      <c r="H68" s="6"/>
-      <c r="I68" s="6"/>
-      <c r="J68" s="6"/>
-      <c r="K68" s="6"/>
-    </row>
-    <row r="69" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="6">
+    </row>
+    <row r="70" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="5">
         <v>65</v>
       </c>
-      <c r="B69" s="6" t="s">
+      <c r="B70" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="C69" s="6">
+      <c r="C70" s="5">
         <v>2</v>
       </c>
-      <c r="D69" s="6" t="s">
+      <c r="D70" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E69" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F69" s="6"/>
-      <c r="G69" s="6"/>
-      <c r="H69" s="6"/>
-      <c r="I69" s="6"/>
-      <c r="J69" s="6"/>
-      <c r="K69" s="6"/>
-    </row>
-    <row r="70" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="6">
+      <c r="E70" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="5">
         <v>66</v>
       </c>
-      <c r="B70" s="6" t="s">
+      <c r="B71" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="C70" s="6">
+      <c r="C71" s="5">
         <v>4</v>
       </c>
-      <c r="D70" s="6" t="s">
+      <c r="D71" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E70" s="6" t="s">
+      <c r="E71" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F70" s="6"/>
-      <c r="G70" s="6"/>
-      <c r="H70" s="6"/>
-      <c r="I70" s="6"/>
-      <c r="J70" s="6"/>
-      <c r="K70" s="6"/>
-    </row>
-    <row r="71" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="6">
+    </row>
+    <row r="72" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="5">
         <v>67</v>
       </c>
-      <c r="B71" s="6" t="s">
+      <c r="B72" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C71" s="6">
+      <c r="C72" s="5">
         <v>4</v>
       </c>
-      <c r="D71" s="6" t="s">
+      <c r="D72" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E71" s="6" t="s">
+      <c r="E72" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F71" s="6"/>
-      <c r="G71" s="6"/>
-      <c r="H71" s="6"/>
-      <c r="I71" s="6"/>
-      <c r="J71" s="6"/>
-      <c r="K71" s="6"/>
-    </row>
-    <row r="72" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="6">
+    </row>
+    <row r="73" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="5">
         <v>68</v>
       </c>
-      <c r="B72" s="6" t="s">
+      <c r="B73" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="C72" s="6">
-        <v>6</v>
-      </c>
-      <c r="D72" s="6" t="s">
+      <c r="C73" s="5">
+        <v>6</v>
+      </c>
+      <c r="D73" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E72" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F72" s="6"/>
-      <c r="G72" s="6"/>
-      <c r="H72" s="6"/>
-      <c r="I72" s="6"/>
-      <c r="J72" s="6"/>
-      <c r="K72" s="6"/>
-    </row>
-    <row r="73" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="6"/>
-      <c r="B73" s="6"/>
-      <c r="C73" s="6"/>
-      <c r="D73" s="6"/>
-      <c r="E73" s="6"/>
-      <c r="F73" s="6"/>
-      <c r="G73" s="6">
+      <c r="E73" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="G74" s="5">
         <v>2</v>
       </c>
-      <c r="H73" s="6" t="s">
+      <c r="H74" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="I73" s="6">
+      <c r="I74" s="5">
         <v>50</v>
       </c>
-      <c r="J73" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="K73" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="74" spans="1:16" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="6"/>
-      <c r="B74" s="6"/>
-      <c r="C74" s="6"/>
-      <c r="D74" s="6"/>
-      <c r="E74" s="6"/>
-      <c r="F74" s="6"/>
-      <c r="G74" s="6">
+      <c r="J74" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="K74" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" s="5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G75" s="5">
         <v>4</v>
       </c>
-      <c r="H74" s="6" t="s">
+      <c r="H75" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="I74" s="6">
-        <v>6</v>
-      </c>
-      <c r="J74" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="K74" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="75" spans="1:16" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="6"/>
-      <c r="B75" s="6"/>
-      <c r="C75" s="6"/>
-      <c r="D75" s="6"/>
-      <c r="E75" s="6"/>
-      <c r="F75" s="6"/>
-      <c r="G75" s="4">
+      <c r="I75" s="5">
+        <v>6</v>
+      </c>
+      <c r="J75" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="K75" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16" s="5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G76" s="3">
         <v>5</v>
       </c>
-      <c r="H75" s="4" t="s">
+      <c r="H76" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="I75" s="4">
+      <c r="I76" s="3">
         <v>150</v>
       </c>
-      <c r="J75" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="K75" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="76" spans="1:16" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="6"/>
-      <c r="B76" s="6"/>
-      <c r="C76" s="6"/>
-      <c r="D76" s="6"/>
-      <c r="E76" s="6"/>
-      <c r="F76" s="6"/>
-      <c r="G76" s="4">
+      <c r="J76" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="K76" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16" s="5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G77" s="3">
         <v>9</v>
       </c>
-      <c r="H76" s="4" t="s">
+      <c r="H77" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="I76" s="4">
+      <c r="I77" s="3">
         <v>4</v>
       </c>
-      <c r="J76" s="6"/>
-      <c r="K76" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="77" spans="1:16" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="6"/>
-      <c r="B77" s="6"/>
-      <c r="C77" s="6"/>
-      <c r="D77" s="6"/>
-      <c r="E77" s="6"/>
-      <c r="F77" s="6"/>
-      <c r="G77" s="4">
+      <c r="K77" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" s="5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G78" s="3">
         <v>10</v>
       </c>
-      <c r="H77" s="4" t="s">
+      <c r="H78" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="I77" s="4">
+      <c r="I78" s="3">
         <v>10</v>
       </c>
-      <c r="J77" s="6"/>
-      <c r="K77" s="6" t="s">
+      <c r="K78" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="78" spans="1:16" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="6"/>
-      <c r="B78" s="6"/>
-      <c r="C78" s="6"/>
-      <c r="D78" s="6"/>
-      <c r="E78" s="6"/>
-      <c r="F78" s="6"/>
-      <c r="G78" s="4">
+    <row r="79" spans="1:16" s="5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G79" s="3">
         <v>11</v>
       </c>
-      <c r="H78" s="4" t="s">
+      <c r="H79" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="I78" s="4">
+      <c r="I79" s="3">
         <v>15</v>
       </c>
-      <c r="J78" s="6"/>
-      <c r="K78" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="79" spans="1:16" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="6"/>
-      <c r="B79" s="6"/>
-      <c r="C79" s="6"/>
-      <c r="D79" s="6"/>
-      <c r="E79" s="6"/>
-      <c r="F79" s="6"/>
-      <c r="G79" s="4">
+      <c r="K79" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16" s="5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G80" s="3">
         <v>16</v>
       </c>
-      <c r="H79" s="4" t="s">
+      <c r="H80" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="I79" s="4">
+      <c r="I80" s="3">
         <v>15</v>
       </c>
-      <c r="J79" s="4"/>
-      <c r="K79" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="L79" s="2"/>
-      <c r="M79" s="2"/>
-      <c r="N79" s="2"/>
-      <c r="O79" s="2"/>
-      <c r="P79" s="2"/>
-    </row>
-    <row r="80" spans="1:16" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="6"/>
-      <c r="B80" s="6"/>
-      <c r="C80" s="6"/>
-      <c r="D80" s="6"/>
-      <c r="E80" s="6"/>
-      <c r="F80" s="6"/>
-      <c r="G80" s="4">
+      <c r="J80" s="3"/>
+      <c r="K80" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L80" s="2"/>
+      <c r="M80" s="2"/>
+      <c r="N80" s="2"/>
+      <c r="O80" s="2"/>
+      <c r="P80" s="2"/>
+    </row>
+    <row r="81" spans="7:11" s="5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G81" s="3">
         <v>27</v>
       </c>
-      <c r="H80" s="4" t="s">
+      <c r="H81" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="I80" s="4">
+      <c r="I81" s="3">
         <v>3</v>
       </c>
-      <c r="J80" s="6"/>
-      <c r="K80" s="6" t="s">
+      <c r="K81" s="5" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="81" spans="1:11" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="6"/>
-      <c r="B81" s="6"/>
-      <c r="C81" s="6"/>
-      <c r="D81" s="6"/>
-      <c r="E81" s="6"/>
-      <c r="F81" s="6"/>
-      <c r="G81" s="4">
+    <row r="82" spans="7:11" s="5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G82" s="3">
         <v>30</v>
       </c>
-      <c r="H81" s="12" t="s">
+      <c r="H82" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="I81" s="4">
+      <c r="I82" s="3">
         <v>8</v>
       </c>
-      <c r="J81" s="6"/>
-      <c r="K81" s="6" t="s">
+      <c r="K82" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="82" spans="1:11" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="6"/>
-      <c r="B82" s="6"/>
-      <c r="C82" s="6"/>
-      <c r="D82" s="6"/>
-      <c r="E82" s="6"/>
-      <c r="F82" s="6"/>
-      <c r="G82" s="4">
+    <row r="83" spans="7:11" s="5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G83" s="3">
         <v>31</v>
       </c>
-      <c r="H82" s="4" t="s">
+      <c r="H83" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="I82" s="4">
-        <v>6</v>
-      </c>
-      <c r="J82" s="6"/>
-      <c r="K82" s="6" t="s">
+      <c r="I83" s="3">
+        <v>6</v>
+      </c>
+      <c r="K83" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="83" spans="1:11" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A83" s="6"/>
-      <c r="B83" s="6"/>
-      <c r="C83" s="6"/>
-      <c r="D83" s="6"/>
-      <c r="E83" s="6"/>
-      <c r="F83" s="6"/>
-      <c r="G83" s="4">
+    <row r="84" spans="7:11" s="5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G84" s="3">
         <v>32</v>
       </c>
-      <c r="H83" s="4" t="s">
+      <c r="H84" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="I83" s="4">
+      <c r="I84" s="3">
         <v>10</v>
       </c>
-      <c r="J83" s="6"/>
-      <c r="K83" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="84" spans="1:11" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="6"/>
-      <c r="B84" s="6"/>
-      <c r="C84" s="6"/>
-      <c r="D84" s="6"/>
-      <c r="E84" s="6"/>
-      <c r="F84" s="6"/>
-      <c r="G84" s="4">
+      <c r="K84" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="85" spans="7:11" s="5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G85" s="3">
         <v>33</v>
       </c>
-      <c r="H84" s="4" t="s">
+      <c r="H85" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="I84" s="4">
+      <c r="I85" s="3">
         <v>4</v>
       </c>
-      <c r="J84" s="6"/>
-      <c r="K84" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="85" spans="1:11" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="6"/>
-      <c r="B85" s="6"/>
-      <c r="C85" s="6"/>
-      <c r="D85" s="6"/>
-      <c r="E85" s="6"/>
-      <c r="F85" s="6"/>
-      <c r="G85" s="4">
+      <c r="K85" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="86" spans="7:11" s="5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G86" s="3">
         <v>34</v>
       </c>
-      <c r="H85" s="4" t="s">
+      <c r="H86" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="I85" s="4">
+      <c r="I86" s="3">
         <v>100</v>
       </c>
-      <c r="J85" s="6"/>
-      <c r="K85" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="6"/>
-      <c r="B86" s="6"/>
-      <c r="C86" s="6"/>
-      <c r="D86" s="6"/>
-      <c r="E86" s="6"/>
-      <c r="F86" s="6"/>
-      <c r="G86" s="4">
+      <c r="K86" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="87" spans="7:11" s="5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G87" s="3">
         <v>35</v>
       </c>
-      <c r="H86" s="12" t="s">
+      <c r="H87" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="I86" s="4">
-        <v>6</v>
-      </c>
-      <c r="J86" s="6"/>
-      <c r="K86" s="6" t="s">
+      <c r="I87" s="3">
+        <v>6</v>
+      </c>
+      <c r="K87" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="87" spans="1:11" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="6"/>
-      <c r="B87" s="6"/>
-      <c r="C87" s="6"/>
-      <c r="D87" s="6"/>
-      <c r="E87" s="6"/>
-      <c r="F87" s="6"/>
-      <c r="G87" s="4">
+    <row r="88" spans="7:11" s="5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G88" s="3">
         <v>36</v>
       </c>
-      <c r="H87" s="12" t="s">
+      <c r="H88" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="I87" s="4">
+      <c r="I88" s="3">
         <v>4</v>
       </c>
-      <c r="J87" s="6"/>
-      <c r="K87" s="6" t="s">
+      <c r="K88" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="88" spans="1:11" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="6"/>
-      <c r="B88" s="6"/>
-      <c r="C88" s="6"/>
-      <c r="D88" s="6"/>
-      <c r="E88" s="6"/>
-      <c r="F88" s="6"/>
-      <c r="G88" s="4">
+    <row r="89" spans="7:11" s="5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G89" s="3">
         <v>37</v>
       </c>
-      <c r="H88" s="4" t="s">
+      <c r="H89" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="I88" s="4">
-        <v>6</v>
-      </c>
-      <c r="J88" s="6"/>
-      <c r="K88" s="6" t="s">
+      <c r="I89" s="3">
+        <v>6</v>
+      </c>
+      <c r="K89" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="89" spans="1:11" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="6"/>
-      <c r="B89" s="6"/>
-      <c r="C89" s="6"/>
-      <c r="D89" s="6"/>
-      <c r="E89" s="6"/>
-      <c r="F89" s="6"/>
-      <c r="G89" s="4">
+    <row r="90" spans="7:11" s="5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G90" s="3">
         <v>38</v>
       </c>
-      <c r="H89" s="4" t="s">
+      <c r="H90" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="I89" s="4">
+      <c r="I90" s="3">
         <v>3</v>
       </c>
-      <c r="J89" s="6"/>
-      <c r="K89" s="6" t="s">
+      <c r="K90" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="90" spans="1:11" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="6"/>
-      <c r="B90" s="6"/>
-      <c r="C90" s="6"/>
-      <c r="D90" s="6"/>
-      <c r="E90" s="6"/>
-      <c r="F90" s="6"/>
-      <c r="G90" s="4">
+    <row r="91" spans="7:11" s="5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G91" s="3">
         <v>39</v>
       </c>
-      <c r="H90" s="11" t="s">
+      <c r="H91" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="I90" s="4">
+      <c r="I91" s="3">
         <v>5</v>
       </c>
-      <c r="J90" s="6"/>
-      <c r="K90" s="6" t="s">
+      <c r="K91" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="91" spans="1:11" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A91" s="6"/>
-      <c r="B91" s="6"/>
-      <c r="C91" s="6"/>
-      <c r="D91" s="6"/>
-      <c r="E91" s="6"/>
-      <c r="F91" s="6"/>
-      <c r="G91" s="4">
+    <row r="92" spans="7:11" s="5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G92" s="3">
         <v>40</v>
       </c>
-      <c r="H91" s="4" t="s">
+      <c r="H92" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="I91" s="4">
+      <c r="I92" s="3">
         <v>2</v>
       </c>
-      <c r="J91" s="6"/>
-      <c r="K91" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="92" spans="1:11" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="6"/>
-      <c r="B92" s="6"/>
-      <c r="C92" s="6"/>
-      <c r="D92" s="6"/>
-      <c r="E92" s="6"/>
-      <c r="F92" s="6"/>
-      <c r="G92" s="4">
+      <c r="K92" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="93" spans="7:11" s="5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G93" s="3">
         <v>41</v>
       </c>
-      <c r="H92" s="4" t="s">
+      <c r="H93" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="I92" s="4">
-        <v>6</v>
-      </c>
-      <c r="J92" s="6"/>
-      <c r="K92" s="6" t="s">
+      <c r="I93" s="3">
+        <v>6</v>
+      </c>
+      <c r="K93" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="93" spans="1:11" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="6"/>
-      <c r="B93" s="6"/>
-      <c r="C93" s="6"/>
-      <c r="D93" s="6"/>
-      <c r="E93" s="6"/>
-      <c r="F93" s="6"/>
-      <c r="G93" s="4">
+    <row r="94" spans="7:11" s="5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G94" s="3">
         <v>42</v>
       </c>
-      <c r="H93" s="4" t="s">
+      <c r="H94" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="I93" s="4">
-        <v>6</v>
-      </c>
-      <c r="J93" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="K93" s="6" t="s">
+      <c r="I94" s="3">
+        <v>6</v>
+      </c>
+      <c r="J94" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="K94" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="94" spans="1:11" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="6"/>
-      <c r="B94" s="6"/>
-      <c r="C94" s="6"/>
-      <c r="D94" s="6"/>
-      <c r="E94" s="6"/>
-      <c r="F94" s="6"/>
-      <c r="G94" s="4">
+    <row r="95" spans="7:11" s="5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G95" s="3">
         <v>45</v>
       </c>
-      <c r="H94" s="4" t="s">
+      <c r="H95" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="I94" s="4">
+      <c r="I95" s="3">
         <v>5</v>
       </c>
-      <c r="J94" s="6"/>
-      <c r="K94" s="6" t="s">
+      <c r="K95" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="95" spans="1:11" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="6"/>
-      <c r="B95" s="6"/>
-      <c r="C95" s="6"/>
-      <c r="D95" s="6"/>
-      <c r="E95" s="6"/>
-      <c r="F95" s="6"/>
-      <c r="G95" s="4">
+    <row r="96" spans="7:11" s="5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G96" s="3">
         <v>46</v>
       </c>
-      <c r="H95" s="4" t="s">
+      <c r="H96" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="I95" s="4">
+      <c r="I96" s="3">
         <v>5</v>
       </c>
-      <c r="J95" s="6"/>
-      <c r="K95" s="6" t="s">
+      <c r="K96" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="96" spans="1:11" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="6"/>
-      <c r="B96" s="6"/>
-      <c r="C96" s="6"/>
-      <c r="D96" s="6"/>
-      <c r="E96" s="6"/>
-      <c r="F96" s="6"/>
-      <c r="G96" s="4">
+    <row r="97" spans="7:11" s="5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G97" s="3">
         <v>47</v>
       </c>
-      <c r="H96" s="4" t="s">
+      <c r="H97" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="I96" s="4">
+      <c r="I97" s="3">
         <v>4</v>
       </c>
-      <c r="J96" s="6"/>
-      <c r="K96" s="6" t="s">
+      <c r="K97" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="97" spans="1:11" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="6"/>
-      <c r="B97" s="6"/>
-      <c r="C97" s="6"/>
-      <c r="D97" s="6"/>
-      <c r="E97" s="6"/>
-      <c r="F97" s="6"/>
-      <c r="G97" s="4">
+    <row r="98" spans="7:11" s="5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G98" s="3">
         <v>50</v>
       </c>
-      <c r="H97" s="4" t="s">
+      <c r="H98" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="I97" s="4">
+      <c r="I98" s="3">
         <v>5</v>
       </c>
-      <c r="J97" s="6"/>
-      <c r="K97" s="6" t="s">
+      <c r="K98" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="98" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="6"/>
-      <c r="B98" s="6"/>
-      <c r="C98" s="6"/>
-      <c r="D98" s="6"/>
-      <c r="E98" s="6"/>
-      <c r="F98" s="6"/>
-      <c r="G98" s="4">
+    <row r="99" spans="7:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="G99" s="3">
         <v>53</v>
       </c>
-      <c r="H98" s="4" t="s">
+      <c r="H99" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="I98" s="4">
+      <c r="I99" s="3">
         <v>500</v>
       </c>
-      <c r="J98" s="6"/>
-      <c r="K98" s="6" t="s">
+      <c r="K99" s="5" t="s">
         <v>7</v>
       </c>
     </row>
@@ -6774,16 +6329,16 @@
   <mergeCells count="12">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="G1:K1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="D19:D20"/>
-    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="E20:E21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -6803,9 +6358,9 @@
               </from>
               <to>
                 <xdr:col>16</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
+                <xdr:colOff>257175</xdr:colOff>
                 <xdr:row>3</xdr:row>
-                <xdr:rowOff>53340</xdr:rowOff>
+                <xdr:rowOff>76200</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -6823,14 +6378,14 @@
               <from>
                 <xdr:col>16</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>3</xdr:row>
+                <xdr:row>4</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>16</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>4</xdr:row>
-                <xdr:rowOff>60960</xdr:rowOff>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>76200</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -6848,14 +6403,14 @@
               <from>
                 <xdr:col>16</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>4</xdr:row>
+                <xdr:row>5</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>16</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>5</xdr:row>
-                <xdr:rowOff>60960</xdr:rowOff>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>6</xdr:row>
+                <xdr:rowOff>76200</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -6873,14 +6428,14 @@
               <from>
                 <xdr:col>16</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>5</xdr:row>
+                <xdr:row>6</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>16</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>6</xdr:row>
-                <xdr:rowOff>60960</xdr:rowOff>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>7</xdr:row>
+                <xdr:rowOff>76200</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -6898,14 +6453,14 @@
               <from>
                 <xdr:col>16</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>6</xdr:row>
+                <xdr:row>7</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>16</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>7</xdr:row>
-                <xdr:rowOff>60960</xdr:rowOff>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>8</xdr:row>
+                <xdr:rowOff>76200</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -6923,14 +6478,14 @@
               <from>
                 <xdr:col>16</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>7</xdr:row>
+                <xdr:row>8</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>16</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>8</xdr:row>
-                <xdr:rowOff>60960</xdr:rowOff>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>9</xdr:row>
+                <xdr:rowOff>76200</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -6948,14 +6503,14 @@
               <from>
                 <xdr:col>16</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>8</xdr:row>
+                <xdr:row>9</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>16</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>9</xdr:row>
-                <xdr:rowOff>60960</xdr:rowOff>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>10</xdr:row>
+                <xdr:rowOff>76200</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -6973,14 +6528,14 @@
               <from>
                 <xdr:col>16</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>9</xdr:row>
+                <xdr:row>10</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>16</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>10</xdr:row>
-                <xdr:rowOff>53340</xdr:rowOff>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>11</xdr:row>
+                <xdr:rowOff>66675</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -6998,14 +6553,14 @@
               <from>
                 <xdr:col>16</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>10</xdr:row>
+                <xdr:row>11</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>16</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>11</xdr:row>
-                <xdr:rowOff>53340</xdr:rowOff>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>12</xdr:row>
+                <xdr:rowOff>66675</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -7023,14 +6578,14 @@
               <from>
                 <xdr:col>16</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>11</xdr:row>
+                <xdr:row>12</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>16</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>12</xdr:row>
-                <xdr:rowOff>53340</xdr:rowOff>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>13</xdr:row>
+                <xdr:rowOff>66675</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -7048,14 +6603,14 @@
               <from>
                 <xdr:col>16</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>12</xdr:row>
+                <xdr:row>13</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>16</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>13</xdr:row>
-                <xdr:rowOff>53340</xdr:rowOff>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>14</xdr:row>
+                <xdr:rowOff>66675</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -7073,14 +6628,14 @@
               <from>
                 <xdr:col>16</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>13</xdr:row>
+                <xdr:row>14</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>16</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>14</xdr:row>
-                <xdr:rowOff>53340</xdr:rowOff>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>15</xdr:row>
+                <xdr:rowOff>66675</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -7098,14 +6653,14 @@
               <from>
                 <xdr:col>16</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>14</xdr:row>
+                <xdr:row>15</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>16</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>15</xdr:row>
-                <xdr:rowOff>53340</xdr:rowOff>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>16</xdr:row>
+                <xdr:rowOff>66675</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -7123,14 +6678,14 @@
               <from>
                 <xdr:col>16</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>15</xdr:row>
+                <xdr:row>16</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>16</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>16</xdr:row>
-                <xdr:rowOff>53340</xdr:rowOff>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>17</xdr:row>
+                <xdr:rowOff>66675</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -7148,14 +6703,14 @@
               <from>
                 <xdr:col>16</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>17</xdr:row>
+                <xdr:row>18</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>16</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>18</xdr:row>
-                <xdr:rowOff>53340</xdr:rowOff>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>19</xdr:row>
+                <xdr:rowOff>66675</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -7173,14 +6728,14 @@
               <from>
                 <xdr:col>16</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>18</xdr:row>
+                <xdr:row>19</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>16</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>19</xdr:row>
-                <xdr:rowOff>53340</xdr:rowOff>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>20</xdr:row>
+                <xdr:rowOff>66675</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -7198,14 +6753,14 @@
               <from>
                 <xdr:col>16</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>20</xdr:row>
+                <xdr:row>21</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>16</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>21</xdr:row>
-                <xdr:rowOff>53340</xdr:rowOff>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>22</xdr:row>
+                <xdr:rowOff>66675</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -7223,14 +6778,14 @@
               <from>
                 <xdr:col>16</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>21</xdr:row>
+                <xdr:row>22</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>16</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>22</xdr:row>
-                <xdr:rowOff>53340</xdr:rowOff>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>23</xdr:row>
+                <xdr:rowOff>66675</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -7248,14 +6803,14 @@
               <from>
                 <xdr:col>16</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>22</xdr:row>
+                <xdr:row>23</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>16</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>23</xdr:row>
-                <xdr:rowOff>60960</xdr:rowOff>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>24</xdr:row>
+                <xdr:rowOff>76200</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -7273,14 +6828,14 @@
               <from>
                 <xdr:col>16</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>23</xdr:row>
+                <xdr:row>24</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>16</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>24</xdr:row>
-                <xdr:rowOff>60960</xdr:rowOff>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>25</xdr:row>
+                <xdr:rowOff>76200</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -7298,14 +6853,14 @@
               <from>
                 <xdr:col>16</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>24</xdr:row>
+                <xdr:row>25</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>16</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>25</xdr:row>
-                <xdr:rowOff>53340</xdr:rowOff>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>26</xdr:row>
+                <xdr:rowOff>66675</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -7323,14 +6878,14 @@
               <from>
                 <xdr:col>16</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>25</xdr:row>
+                <xdr:row>26</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>16</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>26</xdr:row>
-                <xdr:rowOff>53340</xdr:rowOff>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>27</xdr:row>
+                <xdr:rowOff>66675</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -7348,14 +6903,14 @@
               <from>
                 <xdr:col>16</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>26</xdr:row>
+                <xdr:row>27</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>16</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>27</xdr:row>
-                <xdr:rowOff>53340</xdr:rowOff>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>28</xdr:row>
+                <xdr:rowOff>66675</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -7373,14 +6928,14 @@
               <from>
                 <xdr:col>16</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>27</xdr:row>
+                <xdr:row>28</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>16</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>28</xdr:row>
-                <xdr:rowOff>60960</xdr:rowOff>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>29</xdr:row>
+                <xdr:rowOff>76200</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -7398,14 +6953,14 @@
               <from>
                 <xdr:col>16</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>28</xdr:row>
+                <xdr:row>29</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>16</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>29</xdr:row>
-                <xdr:rowOff>60960</xdr:rowOff>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>30</xdr:row>
+                <xdr:rowOff>76200</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -7423,14 +6978,14 @@
               <from>
                 <xdr:col>16</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>29</xdr:row>
+                <xdr:row>30</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>16</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>30</xdr:row>
-                <xdr:rowOff>60960</xdr:rowOff>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>31</xdr:row>
+                <xdr:rowOff>76200</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -7448,14 +7003,14 @@
               <from>
                 <xdr:col>16</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>30</xdr:row>
+                <xdr:row>31</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>16</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>31</xdr:row>
-                <xdr:rowOff>60960</xdr:rowOff>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>32</xdr:row>
+                <xdr:rowOff>76200</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -7473,14 +7028,14 @@
               <from>
                 <xdr:col>16</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>31</xdr:row>
+                <xdr:row>32</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>16</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>32</xdr:row>
-                <xdr:rowOff>53340</xdr:rowOff>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>33</xdr:row>
+                <xdr:rowOff>66675</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -7498,14 +7053,14 @@
               <from>
                 <xdr:col>16</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>32</xdr:row>
+                <xdr:row>33</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>16</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>33</xdr:row>
-                <xdr:rowOff>60960</xdr:rowOff>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>34</xdr:row>
+                <xdr:rowOff>76200</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -7523,14 +7078,14 @@
               <from>
                 <xdr:col>16</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>33</xdr:row>
+                <xdr:row>34</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>16</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>34</xdr:row>
-                <xdr:rowOff>60960</xdr:rowOff>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>35</xdr:row>
+                <xdr:rowOff>76200</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -7548,14 +7103,14 @@
               <from>
                 <xdr:col>16</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>34</xdr:row>
+                <xdr:row>35</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>16</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>35</xdr:row>
-                <xdr:rowOff>53340</xdr:rowOff>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>36</xdr:row>
+                <xdr:rowOff>66675</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -7573,14 +7128,14 @@
               <from>
                 <xdr:col>16</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>35</xdr:row>
+                <xdr:row>36</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>16</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>36</xdr:row>
-                <xdr:rowOff>53340</xdr:rowOff>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>37</xdr:row>
+                <xdr:rowOff>66675</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -7598,14 +7153,14 @@
               <from>
                 <xdr:col>16</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>36</xdr:row>
+                <xdr:row>37</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>16</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>37</xdr:row>
-                <xdr:rowOff>60960</xdr:rowOff>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>38</xdr:row>
+                <xdr:rowOff>76200</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -7623,14 +7178,14 @@
               <from>
                 <xdr:col>16</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>37</xdr:row>
+                <xdr:row>38</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>16</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>38</xdr:row>
-                <xdr:rowOff>60960</xdr:rowOff>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>39</xdr:row>
+                <xdr:rowOff>76200</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -7648,14 +7203,14 @@
               <from>
                 <xdr:col>16</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>38</xdr:row>
+                <xdr:row>39</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>16</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>39</xdr:row>
-                <xdr:rowOff>60960</xdr:rowOff>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>40</xdr:row>
+                <xdr:rowOff>76200</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -7673,14 +7228,14 @@
               <from>
                 <xdr:col>16</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>39</xdr:row>
+                <xdr:row>40</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>16</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>40</xdr:row>
-                <xdr:rowOff>60960</xdr:rowOff>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>41</xdr:row>
+                <xdr:rowOff>76200</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -7698,14 +7253,14 @@
               <from>
                 <xdr:col>16</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>40</xdr:row>
+                <xdr:row>41</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>16</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>41</xdr:row>
-                <xdr:rowOff>60960</xdr:rowOff>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>42</xdr:row>
+                <xdr:rowOff>76200</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -7723,14 +7278,14 @@
               <from>
                 <xdr:col>16</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>41</xdr:row>
+                <xdr:row>42</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>16</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>42</xdr:row>
-                <xdr:rowOff>60960</xdr:rowOff>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>43</xdr:row>
+                <xdr:rowOff>76200</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -7748,14 +7303,14 @@
               <from>
                 <xdr:col>16</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>42</xdr:row>
+                <xdr:row>43</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>16</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>43</xdr:row>
-                <xdr:rowOff>60960</xdr:rowOff>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>44</xdr:row>
+                <xdr:rowOff>76200</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -7773,14 +7328,14 @@
               <from>
                 <xdr:col>16</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>43</xdr:row>
+                <xdr:row>44</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>16</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>44</xdr:row>
-                <xdr:rowOff>60960</xdr:rowOff>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>45</xdr:row>
+                <xdr:rowOff>76200</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -7798,14 +7353,14 @@
               <from>
                 <xdr:col>16</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>44</xdr:row>
+                <xdr:row>45</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>16</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>45</xdr:row>
-                <xdr:rowOff>60960</xdr:rowOff>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>46</xdr:row>
+                <xdr:rowOff>76200</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -7823,14 +7378,14 @@
               <from>
                 <xdr:col>16</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>45</xdr:row>
+                <xdr:row>46</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>16</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>46</xdr:row>
-                <xdr:rowOff>60960</xdr:rowOff>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>47</xdr:row>
+                <xdr:rowOff>76200</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -7848,14 +7403,14 @@
               <from>
                 <xdr:col>16</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>46</xdr:row>
+                <xdr:row>47</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>16</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>47</xdr:row>
-                <xdr:rowOff>60960</xdr:rowOff>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>48</xdr:row>
+                <xdr:rowOff>76200</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -7873,14 +7428,14 @@
               <from>
                 <xdr:col>16</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>47</xdr:row>
+                <xdr:row>48</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>16</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>48</xdr:row>
-                <xdr:rowOff>60960</xdr:rowOff>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>49</xdr:row>
+                <xdr:rowOff>76200</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -7898,14 +7453,14 @@
               <from>
                 <xdr:col>16</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>48</xdr:row>
+                <xdr:row>49</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>16</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>49</xdr:row>
-                <xdr:rowOff>60960</xdr:rowOff>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>50</xdr:row>
+                <xdr:rowOff>76200</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -7923,14 +7478,14 @@
               <from>
                 <xdr:col>16</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>49</xdr:row>
+                <xdr:row>50</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>16</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>50</xdr:row>
-                <xdr:rowOff>60960</xdr:rowOff>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>51</xdr:row>
+                <xdr:rowOff>76200</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -7948,14 +7503,14 @@
               <from>
                 <xdr:col>16</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>50</xdr:row>
+                <xdr:row>51</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>16</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>51</xdr:row>
-                <xdr:rowOff>60960</xdr:rowOff>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>52</xdr:row>
+                <xdr:rowOff>76200</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -7973,14 +7528,14 @@
               <from>
                 <xdr:col>16</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>51</xdr:row>
+                <xdr:row>52</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>16</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>52</xdr:row>
-                <xdr:rowOff>60960</xdr:rowOff>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>53</xdr:row>
+                <xdr:rowOff>76200</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -7998,14 +7553,14 @@
               <from>
                 <xdr:col>16</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>52</xdr:row>
+                <xdr:row>53</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>16</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>53</xdr:row>
-                <xdr:rowOff>60960</xdr:rowOff>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>54</xdr:row>
+                <xdr:rowOff>76200</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -8023,14 +7578,14 @@
               <from>
                 <xdr:col>16</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>53</xdr:row>
+                <xdr:row>54</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>16</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>54</xdr:row>
-                <xdr:rowOff>60960</xdr:rowOff>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>55</xdr:row>
+                <xdr:rowOff>76200</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -8048,14 +7603,14 @@
               <from>
                 <xdr:col>16</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>54</xdr:row>
+                <xdr:row>55</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>16</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>55</xdr:row>
-                <xdr:rowOff>60960</xdr:rowOff>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>56</xdr:row>
+                <xdr:rowOff>76200</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -8073,14 +7628,14 @@
               <from>
                 <xdr:col>16</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>55</xdr:row>
+                <xdr:row>56</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>16</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>56</xdr:row>
-                <xdr:rowOff>60960</xdr:rowOff>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>57</xdr:row>
+                <xdr:rowOff>76200</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -8098,14 +7653,14 @@
               <from>
                 <xdr:col>16</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>56</xdr:row>
+                <xdr:row>57</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>16</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>57</xdr:row>
-                <xdr:rowOff>53340</xdr:rowOff>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>58</xdr:row>
+                <xdr:rowOff>66675</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -8121,30 +7676,30 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K34"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:K35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.88671875" customWidth="1"/>
+    <col min="2" max="2" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="G1" s="9" t="s">
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="G1" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -8176,7 +7731,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -8192,94 +7747,93 @@
       <c r="E3" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3">
         <v>1</v>
       </c>
-      <c r="H3" s="3" t="str">
-        <f>D3</f>
-        <v>Yes</v>
-      </c>
-      <c r="I3" s="3">
+      <c r="H3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3">
         <v>2</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="7">
+      <c r="J3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" s="5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
         <v>2</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C4" s="5">
+        <v>2</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="G4" s="5">
+        <v>2</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="I4" s="5">
+        <v>2</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C5" s="5">
         <v>1</v>
       </c>
-      <c r="D4" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="7" t="s">
+      <c r="D5" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="4">
-        <v>6</v>
-      </c>
-      <c r="H4" s="4" t="s">
+      <c r="G5" s="3">
+        <v>6</v>
+      </c>
+      <c r="H5" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="I4" s="4">
+      <c r="I5" s="3">
         <v>2</v>
       </c>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6" t="s">
+      <c r="J5" s="5"/>
+      <c r="K5" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5">
-        <v>6</v>
-      </c>
-      <c r="D5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" t="s">
-        <v>7</v>
-      </c>
-      <c r="G5" s="3">
-        <v>3</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I5" s="3">
-        <v>6</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D6" t="s">
         <v>6</v>
@@ -8287,94 +7841,109 @@
       <c r="E6" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="3">
-        <v>7</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I6" s="3">
-        <v>6</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6" t="s">
+        <v>10</v>
+      </c>
+      <c r="I6">
+        <v>6</v>
+      </c>
+      <c r="J6" t="s">
+        <v>6</v>
+      </c>
+      <c r="K6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7">
+        <v>4</v>
+      </c>
+      <c r="D7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" t="s">
+        <v>7</v>
+      </c>
+      <c r="G7">
+        <v>7</v>
+      </c>
+      <c r="H7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I7">
+        <v>6</v>
+      </c>
+      <c r="J7" t="s">
+        <v>6</v>
+      </c>
+      <c r="K7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
         <v>12</v>
       </c>
-      <c r="C7">
-        <v>6</v>
-      </c>
-      <c r="D7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G7" s="3">
+      <c r="C8">
+        <v>6</v>
+      </c>
+      <c r="D8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" t="s">
+        <v>7</v>
+      </c>
+      <c r="G8">
         <v>8</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="H8" t="s">
         <v>12</v>
       </c>
-      <c r="I7" s="3">
+      <c r="I8">
         <v>15</v>
       </c>
-      <c r="J7" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="J8" t="s">
+        <v>6</v>
+      </c>
+      <c r="K8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
         <v>13</v>
       </c>
-      <c r="C8">
+      <c r="C9">
         <v>3</v>
-      </c>
-      <c r="D8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9">
-        <v>2</v>
       </c>
       <c r="D9" t="s">
         <v>14</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C10">
         <v>2</v>
@@ -8386,40 +7955,29 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D11" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E11" t="s">
         <v>7</v>
       </c>
-      <c r="G11" s="4">
-        <v>13</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="I11" s="4">
-        <v>15</v>
-      </c>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C12">
         <v>6</v>
@@ -8428,50 +7986,61 @@
         <v>6</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G12" s="3">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I12" s="3">
-        <v>20</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C13">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D13" t="s">
         <v>6</v>
       </c>
       <c r="E13" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+      <c r="G13">
+        <v>2</v>
+      </c>
+      <c r="H13" t="s">
+        <v>122</v>
+      </c>
+      <c r="I13">
+        <v>20</v>
+      </c>
+      <c r="J13" t="s">
+        <v>6</v>
+      </c>
+      <c r="K13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>83</v>
+        <v>19</v>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D14" t="s">
         <v>6</v>
@@ -8480,15 +8049,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C15">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D15" t="s">
         <v>6</v>
@@ -8496,31 +8065,16 @@
       <c r="E15" t="s">
         <v>7</v>
       </c>
-      <c r="G15" s="3">
-        <v>3</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="I15" s="3">
-        <v>250</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C16">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D16" t="s">
         <v>6</v>
@@ -8528,82 +8082,97 @@
       <c r="E16" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G16">
+        <v>3</v>
+      </c>
+      <c r="H16" t="s">
+        <v>154</v>
+      </c>
+      <c r="I16">
+        <v>250</v>
+      </c>
+      <c r="J16" t="s">
+        <v>6</v>
+      </c>
+      <c r="K16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C17">
         <v>2</v>
       </c>
       <c r="D17" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E17" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C18">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D18" t="s">
         <v>14</v>
       </c>
       <c r="E18" t="s">
-        <v>68</v>
-      </c>
-      <c r="G18" s="3">
-        <v>9</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="I18" s="3">
-        <v>9</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C19">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D19" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E19" t="s">
+        <v>68</v>
+      </c>
+      <c r="G19">
         <v>9</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="H19" t="s">
+        <v>159</v>
+      </c>
+      <c r="I19">
+        <v>9</v>
+      </c>
+      <c r="J19" t="s">
+        <v>6</v>
+      </c>
+      <c r="K19" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D20" t="s">
         <v>6</v>
@@ -8612,162 +8181,161 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C21">
+        <v>3</v>
+      </c>
+      <c r="D21" t="s">
+        <v>6</v>
+      </c>
+      <c r="E21" t="s">
         <v>9</v>
       </c>
-      <c r="D21" t="s">
-        <v>6</v>
-      </c>
-      <c r="E21" t="s">
-        <v>28</v>
-      </c>
-      <c r="G21" s="3">
-        <v>10</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="I21" s="3">
-        <v>9</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C22">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D22" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E22" t="s">
+        <v>28</v>
+      </c>
+      <c r="G22">
+        <v>10</v>
+      </c>
+      <c r="H22" t="s">
+        <v>166</v>
+      </c>
+      <c r="I22">
         <v>9</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="J22" t="s">
+        <v>6</v>
+      </c>
+      <c r="K22" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C23">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D23" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E23" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C24">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D24" t="s">
         <v>6</v>
       </c>
       <c r="E24" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C25">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D25" t="s">
         <v>6</v>
       </c>
       <c r="E25" t="s">
-        <v>9</v>
-      </c>
-      <c r="G25" s="3">
-        <v>6</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="I25" s="3">
-        <v>25</v>
-      </c>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C26">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D26" t="s">
         <v>6</v>
       </c>
       <c r="E26" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+      <c r="G26">
+        <v>6</v>
+      </c>
+      <c r="H26" t="s">
+        <v>157</v>
+      </c>
+      <c r="I26">
+        <v>25</v>
+      </c>
+      <c r="K26" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C27">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D27" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E27" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C28">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D28" t="s">
         <v>14</v>
@@ -8776,95 +8344,107 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="G29" s="3">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>27</v>
+      </c>
+      <c r="B29" t="s">
+        <v>97</v>
+      </c>
+      <c r="C29">
+        <v>2</v>
+      </c>
+      <c r="D29" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G30">
         <v>4</v>
       </c>
-      <c r="H29" s="3" t="s">
+      <c r="H30" t="s">
         <v>155</v>
       </c>
-      <c r="I29" s="3">
+      <c r="I30">
         <v>2</v>
       </c>
-      <c r="J29" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="K29" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="G30" s="3">
+      <c r="J30" t="s">
+        <v>6</v>
+      </c>
+      <c r="K30" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G31">
         <v>11</v>
       </c>
-      <c r="H30" s="3" t="s">
+      <c r="H31" t="s">
         <v>160</v>
       </c>
-      <c r="I30" s="3">
+      <c r="I31">
         <v>12</v>
       </c>
-      <c r="J30" s="3"/>
-      <c r="K30" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="G31" s="3">
+      <c r="K31" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G32">
         <v>12</v>
       </c>
-      <c r="H31" s="3" t="s">
+      <c r="H32" t="s">
         <v>161</v>
       </c>
-      <c r="I31" s="3">
+      <c r="I32">
         <v>2</v>
       </c>
-      <c r="J31" s="3"/>
-      <c r="K31" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="G32" s="3">
+      <c r="K32" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="7:11" x14ac:dyDescent="0.25">
+      <c r="G33">
         <v>13</v>
       </c>
-      <c r="H32" s="3" t="s">
+      <c r="H33" t="s">
         <v>162</v>
       </c>
-      <c r="I32" s="3">
+      <c r="I33">
         <v>4</v>
       </c>
-      <c r="J32" s="3"/>
-      <c r="K32" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="33" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G33" s="3">
+      <c r="K33" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="7:11" x14ac:dyDescent="0.25">
+      <c r="G34">
         <v>14</v>
       </c>
-      <c r="H33" s="3" t="s">
+      <c r="H34" t="s">
         <v>163</v>
       </c>
-      <c r="I33" s="3">
+      <c r="I34">
         <v>5</v>
       </c>
-      <c r="J33" s="3"/>
-      <c r="K33" s="3" t="s">
+      <c r="K34" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="34" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="G34" s="3">
+    <row r="35" spans="7:11" x14ac:dyDescent="0.25">
+      <c r="G35">
         <v>15</v>
       </c>
-      <c r="H34" s="3" t="s">
+      <c r="H35" t="s">
         <v>164</v>
       </c>
-      <c r="I34" s="3">
+      <c r="I35">
         <v>8</v>
       </c>
-      <c r="J34" s="3"/>
-      <c r="K34" s="3" t="s">
+      <c r="K35" t="s">
         <v>7</v>
       </c>
     </row>
@@ -8880,776 +8460,809 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:K34"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:K35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.5546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.44140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.109375" style="3"/>
-    <col min="7" max="7" width="3.5546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.5546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.44140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.5546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="G1" s="10" t="s">
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="G1" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" t="s">
         <v>0</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" t="s">
         <v>1</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" t="s">
         <v>2</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" t="s">
         <v>3</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3">
         <v>2</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G3" s="3">
+      <c r="D3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3">
         <v>1</v>
       </c>
-      <c r="H3" s="3" t="str">
-        <f>D3</f>
-        <v>Yes</v>
-      </c>
-      <c r="I3" s="3">
+      <c r="H3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3">
         <v>2</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="6">
+      <c r="J3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" s="5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
         <v>2</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="G4" s="5">
+        <v>2</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="I4" s="5">
+        <v>2</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C5" s="5">
         <v>1</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="6" t="s">
+      <c r="D5" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="6"/>
-      <c r="G4" s="4">
-        <v>6</v>
-      </c>
-      <c r="H4" s="4" t="s">
+      <c r="G5" s="3">
+        <v>6</v>
+      </c>
+      <c r="H5" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="I4" s="4">
+      <c r="I5" s="3">
         <v>2</v>
       </c>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6" t="s">
+      <c r="J5" s="5"/>
+      <c r="K5" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+      <c r="D6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="H6" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="3">
-        <v>6</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G5" s="3">
+      <c r="I6">
+        <v>6</v>
+      </c>
+      <c r="J6" t="s">
+        <v>6</v>
+      </c>
+      <c r="K6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="5">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7">
+        <v>4</v>
+      </c>
+      <c r="D7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" t="s">
+        <v>7</v>
+      </c>
+      <c r="G7">
+        <v>7</v>
+      </c>
+      <c r="H7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I7">
+        <v>6</v>
+      </c>
+      <c r="J7" t="s">
+        <v>6</v>
+      </c>
+      <c r="K7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="5">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8">
+        <v>6</v>
+      </c>
+      <c r="D8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" t="s">
+        <v>7</v>
+      </c>
+      <c r="G8">
+        <v>8</v>
+      </c>
+      <c r="H8" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8">
+        <v>15</v>
+      </c>
+      <c r="J8" t="s">
+        <v>6</v>
+      </c>
+      <c r="K8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9">
         <v>3</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="D9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="5">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+      <c r="D10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" s="5" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11">
+        <v>2</v>
+      </c>
+      <c r="D11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G11"/>
+      <c r="H11"/>
+      <c r="I11"/>
+      <c r="J11"/>
+      <c r="K11"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12">
         <v>10</v>
       </c>
-      <c r="I5" s="3">
-        <v>6</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="3">
+      <c r="B12" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="5">
+        <v>6</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="G12" s="3">
+        <v>13</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="I12" s="3">
+        <v>15</v>
+      </c>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="5">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13">
+        <v>6</v>
+      </c>
+      <c r="D13" t="s">
+        <v>6</v>
+      </c>
+      <c r="E13" t="s">
+        <v>9</v>
+      </c>
+      <c r="G13">
+        <v>2</v>
+      </c>
+      <c r="H13" t="s">
+        <v>122</v>
+      </c>
+      <c r="I13">
+        <v>20</v>
+      </c>
+      <c r="J13" t="s">
+        <v>6</v>
+      </c>
+      <c r="K13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="5">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14">
         <v>4</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="3">
+      <c r="D14" t="s">
+        <v>6</v>
+      </c>
+      <c r="E14" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>83</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="5">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>84</v>
+      </c>
+      <c r="C16">
+        <v>10</v>
+      </c>
+      <c r="D16" t="s">
+        <v>6</v>
+      </c>
+      <c r="E16" t="s">
+        <v>7</v>
+      </c>
+      <c r="G16">
+        <v>3</v>
+      </c>
+      <c r="H16" t="s">
+        <v>154</v>
+      </c>
+      <c r="I16">
+        <v>250</v>
+      </c>
+      <c r="J16" t="s">
+        <v>6</v>
+      </c>
+      <c r="K16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="5">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>98</v>
+      </c>
+      <c r="C17">
+        <v>2</v>
+      </c>
+      <c r="D17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E17" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18" t="s">
+        <v>99</v>
+      </c>
+      <c r="C18">
+        <v>5</v>
+      </c>
+      <c r="D18" t="s">
+        <v>6</v>
+      </c>
+      <c r="E18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="5">
+        <v>17</v>
+      </c>
+      <c r="B19" t="s">
+        <v>93</v>
+      </c>
+      <c r="C19">
+        <v>2</v>
+      </c>
+      <c r="D19" t="s">
+        <v>6</v>
+      </c>
+      <c r="E19" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="5">
+        <v>18</v>
+      </c>
+      <c r="B20" t="s">
+        <v>94</v>
+      </c>
+      <c r="C20">
         <v>4</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G6" s="3">
-        <v>7</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I6" s="3">
-        <v>6</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="3">
+      <c r="D20" t="s">
+        <v>6</v>
+      </c>
+      <c r="E20" t="s">
+        <v>9</v>
+      </c>
+      <c r="G20">
+        <v>6</v>
+      </c>
+      <c r="H20" t="s">
+        <v>157</v>
+      </c>
+      <c r="I20">
+        <v>25</v>
+      </c>
+      <c r="K20" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21" t="s">
+        <v>86</v>
+      </c>
+      <c r="C21">
+        <v>2</v>
+      </c>
+      <c r="D21" t="s">
+        <v>6</v>
+      </c>
+      <c r="E21" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="5">
+        <v>20</v>
+      </c>
+      <c r="B22" t="s">
+        <v>100</v>
+      </c>
+      <c r="C22">
+        <v>4</v>
+      </c>
+      <c r="D22" t="s">
+        <v>6</v>
+      </c>
+      <c r="E22" t="s">
+        <v>7</v>
+      </c>
+      <c r="G22">
+        <v>8</v>
+      </c>
+      <c r="H22" t="s">
+        <v>96</v>
+      </c>
+      <c r="I22">
+        <v>6</v>
+      </c>
+      <c r="K22" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="5">
+        <v>21</v>
+      </c>
+      <c r="B23" t="s">
+        <v>101</v>
+      </c>
+      <c r="C23">
+        <v>2</v>
+      </c>
+      <c r="D23" t="s">
+        <v>6</v>
+      </c>
+      <c r="E23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>22</v>
+      </c>
+      <c r="B24" t="s">
+        <v>102</v>
+      </c>
+      <c r="C24">
+        <v>3</v>
+      </c>
+      <c r="D24" t="s">
+        <v>6</v>
+      </c>
+      <c r="E24" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="5">
+        <v>23</v>
+      </c>
+      <c r="B25" t="s">
+        <v>103</v>
+      </c>
+      <c r="C25">
+        <v>3</v>
+      </c>
+      <c r="D25" t="s">
+        <v>6</v>
+      </c>
+      <c r="E25" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" s="5">
+        <v>24</v>
+      </c>
+      <c r="B26" t="s">
+        <v>104</v>
+      </c>
+      <c r="C26">
+        <v>6</v>
+      </c>
+      <c r="D26" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>25</v>
+      </c>
+      <c r="B27" t="s">
+        <v>105</v>
+      </c>
+      <c r="C27">
+        <v>6</v>
+      </c>
+      <c r="D27" t="s">
+        <v>6</v>
+      </c>
+      <c r="E27" t="s">
+        <v>7</v>
+      </c>
+      <c r="G27">
+        <v>7</v>
+      </c>
+      <c r="H27" t="s">
+        <v>158</v>
+      </c>
+      <c r="I27">
+        <v>4</v>
+      </c>
+      <c r="K27" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="5">
+        <v>26</v>
+      </c>
+      <c r="B28" t="s">
+        <v>106</v>
+      </c>
+      <c r="C28">
+        <v>15</v>
+      </c>
+      <c r="D28" t="s">
+        <v>14</v>
+      </c>
+      <c r="E28" t="s">
+        <v>7</v>
+      </c>
+      <c r="G28">
         <v>5</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="3">
-        <v>6</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G7" s="3">
-        <v>8</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I7" s="3">
-        <v>15</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="3">
-        <v>6</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="3">
-        <v>3</v>
-      </c>
-      <c r="D8" s="3" t="s">
+      <c r="H28" t="s">
+        <v>156</v>
+      </c>
+      <c r="I28">
+        <v>20</v>
+      </c>
+      <c r="K28" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="5">
+        <v>27</v>
+      </c>
+      <c r="B29" t="s">
+        <v>107</v>
+      </c>
+      <c r="C29">
+        <v>2</v>
+      </c>
+      <c r="D29" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="3">
-        <v>7</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="3">
+      <c r="E29" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>28</v>
+      </c>
+      <c r="B30" t="s">
+        <v>108</v>
+      </c>
+      <c r="C30">
         <v>2</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D30" t="s">
         <v>14</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="3">
-        <v>8</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="3">
+      <c r="E30" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" s="5">
+        <v>29</v>
+      </c>
+      <c r="B31" t="s">
+        <v>109</v>
+      </c>
+      <c r="C31">
+        <v>20</v>
+      </c>
+      <c r="D31" t="s">
+        <v>14</v>
+      </c>
+      <c r="E31" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" s="5">
+        <v>30</v>
+      </c>
+      <c r="B32" t="s">
+        <v>110</v>
+      </c>
+      <c r="C32">
+        <v>5</v>
+      </c>
+      <c r="D32" t="s">
+        <v>14</v>
+      </c>
+      <c r="E32" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>31</v>
+      </c>
+      <c r="B33" t="s">
+        <v>111</v>
+      </c>
+      <c r="C33">
+        <v>4</v>
+      </c>
+      <c r="D33" t="s">
+        <v>14</v>
+      </c>
+      <c r="E33" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="5">
+        <v>32</v>
+      </c>
+      <c r="B34" t="s">
+        <v>112</v>
+      </c>
+      <c r="C34">
         <v>2</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D34" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="6">
-        <v>9</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="6">
-        <v>6</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" s="6"/>
-      <c r="G11" s="4">
-        <v>13</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="I11" s="4">
-        <v>15</v>
-      </c>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="3">
-        <v>10</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="3">
-        <v>6</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G12" s="3">
-        <v>2</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="I12" s="3">
-        <v>20</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="3">
-        <v>11</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C13" s="3">
+      <c r="E34" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="5">
+        <v>33</v>
+      </c>
+      <c r="B35" t="s">
+        <v>113</v>
+      </c>
+      <c r="C35">
         <v>4</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="3">
-        <v>12</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C14" s="3">
-        <v>1</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="3">
-        <v>13</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C15" s="3">
-        <v>10</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G15" s="3">
-        <v>3</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="I15" s="3">
-        <v>250</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" s="3">
+      <c r="D35" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C16" s="3">
-        <v>2</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" s="3">
-        <v>15</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C17" s="3">
-        <v>5</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A18" s="3">
-        <v>16</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C18" s="3">
-        <v>2</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" s="3">
-        <v>17</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="C19" s="3">
-        <v>4</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G19" s="3">
-        <v>6</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="I19" s="3">
-        <v>25</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A20" s="3">
-        <v>18</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C20" s="3">
-        <v>2</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A21" s="3">
-        <v>19</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C21" s="3">
-        <v>4</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G21" s="3">
-        <v>8</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="I21" s="3">
-        <v>6</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A22" s="3">
-        <v>20</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="C22" s="3">
-        <v>2</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" s="3">
-        <v>21</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="C23" s="3">
-        <v>3</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A24" s="3">
-        <v>22</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="C24" s="3">
-        <v>3</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A25" s="3">
-        <v>23</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="C25" s="3">
-        <v>6</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A26" s="3">
-        <v>24</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="C26" s="3">
-        <v>6</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G26" s="3">
-        <v>7</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="I26" s="3">
-        <v>4</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A27" s="3">
-        <v>25</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="C27" s="3">
-        <v>15</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G27" s="3">
-        <v>5</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="I27" s="3">
-        <v>20</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A28" s="3">
-        <v>26</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C28" s="3">
-        <v>2</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A29" s="3">
-        <v>27</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C29" s="3">
-        <v>2</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A30" s="3">
-        <v>28</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C30" s="3">
-        <v>20</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A31" s="3">
-        <v>29</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C31" s="3">
-        <v>5</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A32" s="3">
-        <v>30</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C32" s="3">
-        <v>4</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="3">
-        <v>31</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="C33" s="3">
-        <v>2</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" s="3">
-        <v>32</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C34" s="3">
-        <v>4</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E34" s="3" t="s">
+      <c r="E35" t="s">
         <v>68</v>
       </c>
     </row>
